--- a/data/relatorios.xlsx
+++ b/data/relatorios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L298"/>
+  <dimension ref="A1:L484"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -471,8 +471,8 @@
       <c r="K2" t="str">
         <v/>
       </c>
-      <c r="L2" t="str">
-        <v>FALSE</v>
+      <c r="L2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -851,8 +851,8 @@
       <c r="K12" t="str">
         <v/>
       </c>
-      <c r="L12" t="str">
-        <v>FALSE</v>
+      <c r="L12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3929,8 +3929,8 @@
       <c r="K93" t="str">
         <v/>
       </c>
-      <c r="L93" t="str">
-        <v>FALSE</v>
+      <c r="L93" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3967,8 +3967,8 @@
       <c r="K94" t="str">
         <v/>
       </c>
-      <c r="L94" t="str">
-        <v>FALSE</v>
+      <c r="L94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4005,8 +4005,8 @@
       <c r="K95" t="str">
         <v/>
       </c>
-      <c r="L95" t="str">
-        <v>FALSE</v>
+      <c r="L95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4043,8 +4043,8 @@
       <c r="K96" t="str">
         <v/>
       </c>
-      <c r="L96" t="str">
-        <v>FALSE</v>
+      <c r="L96" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4081,8 +4081,8 @@
       <c r="K97" t="str">
         <v/>
       </c>
-      <c r="L97" t="str">
-        <v>FALSE</v>
+      <c r="L97" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -10962,7 +10962,7 @@
         <v/>
       </c>
       <c r="L278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -11000,7 +11000,7 @@
         <v/>
       </c>
       <c r="L279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -11038,7 +11038,7 @@
         <v/>
       </c>
       <c r="L280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -11076,7 +11076,7 @@
         <v/>
       </c>
       <c r="L281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -11114,7 +11114,7 @@
         <v/>
       </c>
       <c r="L282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -11725,9 +11725,7079 @@
         <v>0</v>
       </c>
     </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>C2026.0298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>07/02/2026</v>
+      </c>
+      <c r="C299" t="str">
+        <v>52251531</v>
+      </c>
+      <c r="D299" t="str">
+        <v>PEDALZINHO SX</v>
+      </c>
+      <c r="E299" t="str">
+        <v>6</v>
+      </c>
+      <c r="F299" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G299" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H299" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I299" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J299" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K299" t="str">
+        <v/>
+      </c>
+      <c r="L299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>C2026.0299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C300" t="str">
+        <v>53494305</v>
+      </c>
+      <c r="D300" t="str">
+        <v>APOIO DA LONGARINA LATERAL SX</v>
+      </c>
+      <c r="E300" t="str">
+        <v>7</v>
+      </c>
+      <c r="F300" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G300" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H300" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I300" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J300" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K300" t="str">
+        <v/>
+      </c>
+      <c r="L300" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>C2026.0300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C301" t="str">
+        <v>53494305</v>
+      </c>
+      <c r="D301" t="str">
+        <v>APOIO DA LONGARINA LATERAL SX</v>
+      </c>
+      <c r="E301" t="str">
+        <v>7</v>
+      </c>
+      <c r="F301" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G301" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H301" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I301" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J301" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K301" t="str">
+        <v/>
+      </c>
+      <c r="L301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>C2026.0301</v>
+      </c>
+      <c r="B302" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C302" t="str">
+        <v>534894520</v>
+      </c>
+      <c r="D302" t="str">
+        <v xml:space="preserve">ESPADA SX </v>
+      </c>
+      <c r="E302" t="str">
+        <v>7</v>
+      </c>
+      <c r="F302" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G302" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H302" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I302" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J302" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K302" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="L302" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>C2026.0302</v>
+      </c>
+      <c r="B303" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C303" t="str">
+        <v>53489449</v>
+      </c>
+      <c r="D303" t="str">
+        <v>ESPADA DX</v>
+      </c>
+      <c r="E303" t="str">
+        <v>7</v>
+      </c>
+      <c r="F303" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G303" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H303" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I303" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J303" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K303" t="str">
+        <v/>
+      </c>
+      <c r="L303" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>C2026.0303</v>
+      </c>
+      <c r="B304" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C304" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D304" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E304" t="str">
+        <v>7</v>
+      </c>
+      <c r="F304" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G304" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H304" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I304" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J304" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K304" t="str">
+        <v/>
+      </c>
+      <c r="L304" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>C2026.0304</v>
+      </c>
+      <c r="B305" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C305" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D305" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E305" t="str">
+        <v>7</v>
+      </c>
+      <c r="F305" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G305" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H305" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I305" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J305" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K305" t="str">
+        <v/>
+      </c>
+      <c r="L305" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>C2026.0305</v>
+      </c>
+      <c r="B306" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D306" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E306" t="str">
+        <v>7</v>
+      </c>
+      <c r="F306" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G306" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H306" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I306" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J306" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K306" t="str">
+        <v/>
+      </c>
+      <c r="L306" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>C2026.0306</v>
+      </c>
+      <c r="B307" t="str">
+        <v>09/02/2026</v>
+      </c>
+      <c r="C307" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D307" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E307" t="str">
+        <v>7</v>
+      </c>
+      <c r="F307" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G307" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H307" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I307" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J307" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K307" t="str">
+        <v/>
+      </c>
+      <c r="L307" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>C2026.0307</v>
+      </c>
+      <c r="B308" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C308" t="str">
+        <v>53416455</v>
+      </c>
+      <c r="D308" t="str">
+        <v>CUCÃO SX</v>
+      </c>
+      <c r="E308" t="str">
+        <v>7</v>
+      </c>
+      <c r="F308" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G308" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H308" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I308" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J308" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K308" t="str">
+        <v/>
+      </c>
+      <c r="L308" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>C2026.0308</v>
+      </c>
+      <c r="B309" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C309" t="str">
+        <v>53489536</v>
+      </c>
+      <c r="D309" t="str">
+        <v>FACÃO DX</v>
+      </c>
+      <c r="E309" t="str">
+        <v>7</v>
+      </c>
+      <c r="F309" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G309" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H309" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I309" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J309" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K309" t="str">
+        <v/>
+      </c>
+      <c r="L309" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>C2026.0309</v>
+      </c>
+      <c r="B310" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C310" t="str">
+        <v>53489598</v>
+      </c>
+      <c r="D310" t="str">
+        <v>facão sx</v>
+      </c>
+      <c r="E310" t="str">
+        <v>7</v>
+      </c>
+      <c r="F310" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G310" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H310" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I310" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J310" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K310" t="str">
+        <v/>
+      </c>
+      <c r="L310" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>C2026.0310</v>
+      </c>
+      <c r="B311" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C311" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D311" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E311" t="str">
+        <v>7</v>
+      </c>
+      <c r="F311" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G311" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H311" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I311" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J311" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K311" t="str">
+        <v/>
+      </c>
+      <c r="L311" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>C2026.0311</v>
+      </c>
+      <c r="B312" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C312" t="str">
+        <v>534895350</v>
+      </c>
+      <c r="D312" t="str">
+        <v>SOFAZINHO SX</v>
+      </c>
+      <c r="E312" t="str">
+        <v>7</v>
+      </c>
+      <c r="F312" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G312" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H312" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I312" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J312" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K312" t="str">
+        <v/>
+      </c>
+      <c r="L312" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>C2026.0312</v>
+      </c>
+      <c r="B313" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C313" t="str">
+        <v>53328135</v>
+      </c>
+      <c r="D313" t="str">
+        <v>SOFAZINHO DX</v>
+      </c>
+      <c r="E313" t="str">
+        <v>7</v>
+      </c>
+      <c r="F313" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G313" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H313" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I313" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J313" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K313" t="str">
+        <v/>
+      </c>
+      <c r="L313" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>C2026.0313</v>
+      </c>
+      <c r="B314" t="str">
+        <v>10/02/2026</v>
+      </c>
+      <c r="C314" t="str">
+        <v>534981060</v>
+      </c>
+      <c r="D314" t="str">
+        <v>CUCÃO SX</v>
+      </c>
+      <c r="E314" t="str">
+        <v>7</v>
+      </c>
+      <c r="F314" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G314" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H314" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I314" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J314" t="str">
+        <v>ACOMP PRODUÇÃO 1/400</v>
+      </c>
+      <c r="K314" t="str">
+        <v/>
+      </c>
+      <c r="L314" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>C2026.0314</v>
+      </c>
+      <c r="B315" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C315" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D315" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E315" t="str">
+        <v>7</v>
+      </c>
+      <c r="F315" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G315" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H315" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I315" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J315" t="str">
+        <v>ACOMP PRODUÇÃO 1/400</v>
+      </c>
+      <c r="K315" t="str">
+        <v/>
+      </c>
+      <c r="L315" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>C2026.0315</v>
+      </c>
+      <c r="B316" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C316" t="str">
+        <v>53328128</v>
+      </c>
+      <c r="D316" t="str">
+        <v>PIGMEU DX</v>
+      </c>
+      <c r="E316" t="str">
+        <v>7</v>
+      </c>
+      <c r="F316" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G316" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H316" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I316" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J316" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
+      <c r="L316" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>C2026.0316</v>
+      </c>
+      <c r="B317" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C317" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D317" t="str">
+        <v>BRACKET CATELLO BATTERY</v>
+      </c>
+      <c r="E317" t="str">
+        <v>7</v>
+      </c>
+      <c r="F317" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G317" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H317" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I317" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J317" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
+      <c r="L317" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>C2026.0317</v>
+      </c>
+      <c r="B318" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C318" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D318" t="str">
+        <v>BRACKET CATELLO BATTERY</v>
+      </c>
+      <c r="E318" t="str">
+        <v>7</v>
+      </c>
+      <c r="F318" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G318" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H318" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I318" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J318" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
+      <c r="L318" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>C2026.0318</v>
+      </c>
+      <c r="B319" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C319" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D319" t="str">
+        <v>BRACKET CATELLO BATTERY</v>
+      </c>
+      <c r="E319" t="str">
+        <v>7</v>
+      </c>
+      <c r="F319" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G319" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H319" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I319" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J319" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
+      <c r="L319" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>C2026.0319</v>
+      </c>
+      <c r="B320" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C320" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D320" t="str">
+        <v>BRACKET CATELLO BATTERY</v>
+      </c>
+      <c r="E320" t="str">
+        <v>7</v>
+      </c>
+      <c r="F320" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G320" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H320" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I320" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J320" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
+      <c r="L320" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>C2026.0320</v>
+      </c>
+      <c r="B321" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C321" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D321" t="str">
+        <v>BRACKET CATELLO BATTERY</v>
+      </c>
+      <c r="E321" t="str">
+        <v>7</v>
+      </c>
+      <c r="F321" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G321" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H321" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I321" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J321" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
+      <c r="L321" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>C2026.0321</v>
+      </c>
+      <c r="B322" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C322" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D322" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E322" t="str">
+        <v>7</v>
+      </c>
+      <c r="F322" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G322" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H322" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I322" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J322" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
+      <c r="L322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>C2026.0322</v>
+      </c>
+      <c r="B323" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C323" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D323" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E323" t="str">
+        <v>7</v>
+      </c>
+      <c r="F323" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G323" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H323" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I323" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J323" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
+      <c r="L323" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>C2026.0323</v>
+      </c>
+      <c r="B324" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C324" t="str">
+        <v xml:space="preserve"> 53328129</v>
+      </c>
+      <c r="D324" t="str">
+        <v>PIGMEU SX</v>
+      </c>
+      <c r="E324" t="str">
+        <v>7</v>
+      </c>
+      <c r="F324" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G324" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H324" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I324" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J324" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
+      <c r="L324" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>C2026.0324</v>
+      </c>
+      <c r="B325" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C325" t="str">
+        <v>53489520</v>
+      </c>
+      <c r="D325" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E325" t="str">
+        <v>7</v>
+      </c>
+      <c r="F325" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G325" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H325" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I325" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J325" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
+      <c r="L325" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>C2026.0325</v>
+      </c>
+      <c r="B326" t="str">
+        <v>11/02/2026</v>
+      </c>
+      <c r="C326" t="str">
+        <v>53489591</v>
+      </c>
+      <c r="D326" t="str">
+        <v>TRIDENTE SX</v>
+      </c>
+      <c r="E326" t="str">
+        <v>7</v>
+      </c>
+      <c r="F326" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G326" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H326" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I326" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J326" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>C2026.0326</v>
+      </c>
+      <c r="B327" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C327" t="str">
+        <v>53489521</v>
+      </c>
+      <c r="D327" t="str">
+        <v>TRIDENTE DX</v>
+      </c>
+      <c r="E327" t="str">
+        <v>7</v>
+      </c>
+      <c r="F327" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G327" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H327" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I327" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J327" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K327" t="str">
+        <v/>
+      </c>
+      <c r="L327" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>C2026.0327</v>
+      </c>
+      <c r="B328" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C328" t="str">
+        <v>53327206</v>
+      </c>
+      <c r="D328" t="str">
+        <v>MACAQUINHO SX</v>
+      </c>
+      <c r="E328" t="str">
+        <v>7</v>
+      </c>
+      <c r="F328" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G328" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H328" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I328" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J328" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K328" t="str">
+        <v/>
+      </c>
+      <c r="L328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>C2026.0328</v>
+      </c>
+      <c r="B329" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C329" t="str">
+        <v>53327206</v>
+      </c>
+      <c r="D329" t="str">
+        <v>MACAQUINHO SX</v>
+      </c>
+      <c r="E329" t="str">
+        <v>7</v>
+      </c>
+      <c r="F329" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G329" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H329" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I329" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J329" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K329" t="str">
+        <v/>
+      </c>
+      <c r="L329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>C2026.0329</v>
+      </c>
+      <c r="B330" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C330" t="str">
+        <v>53327206</v>
+      </c>
+      <c r="D330" t="str">
+        <v>MACAQUINHO SX</v>
+      </c>
+      <c r="E330" t="str">
+        <v>7</v>
+      </c>
+      <c r="F330" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G330" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H330" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I330" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J330" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K330" t="str">
+        <v/>
+      </c>
+      <c r="L330" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>C2026.0330</v>
+      </c>
+      <c r="B331" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C331" t="str">
+        <v>53327206</v>
+      </c>
+      <c r="D331" t="str">
+        <v>MACAQUINHO SX</v>
+      </c>
+      <c r="E331" t="str">
+        <v>7</v>
+      </c>
+      <c r="F331" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G331" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H331" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I331" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J331" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K331" t="str">
+        <v/>
+      </c>
+      <c r="L331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>C2026.0331</v>
+      </c>
+      <c r="B332" t="str">
+        <v>12/02/2026</v>
+      </c>
+      <c r="C332" t="str">
+        <v>53327206</v>
+      </c>
+      <c r="D332" t="str">
+        <v>MACAQUINHO SX</v>
+      </c>
+      <c r="E332" t="str">
+        <v>7</v>
+      </c>
+      <c r="F332" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G332" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H332" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I332" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J332" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K332" t="str">
+        <v/>
+      </c>
+      <c r="L332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>C2026.0332</v>
+      </c>
+      <c r="B333" t="str">
+        <v>13/02/2026</v>
+      </c>
+      <c r="C333" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D333" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E333" t="str">
+        <v>7</v>
+      </c>
+      <c r="F333" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G333" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H333" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I333" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J333" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K333" t="str">
+        <v/>
+      </c>
+      <c r="L333" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>C2026.0333</v>
+      </c>
+      <c r="B334" t="str">
+        <v>13/02/2026</v>
+      </c>
+      <c r="C334" t="str">
+        <v>53489582</v>
+      </c>
+      <c r="D334" t="str">
+        <v>CINTA DX</v>
+      </c>
+      <c r="E334" t="str">
+        <v>7</v>
+      </c>
+      <c r="F334" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G334" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H334" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I334" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J334" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K334" t="str">
+        <v/>
+      </c>
+      <c r="L334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>C2026.0334</v>
+      </c>
+      <c r="B335" t="str">
+        <v>13/02/2026</v>
+      </c>
+      <c r="C335" t="str">
+        <v>53489581</v>
+      </c>
+      <c r="D335" t="str">
+        <v>cinta dx</v>
+      </c>
+      <c r="E335" t="str">
+        <v>7</v>
+      </c>
+      <c r="F335" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G335" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H335" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I335" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J335" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K335" t="str">
+        <v/>
+      </c>
+      <c r="L335" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>C2026.0335</v>
+      </c>
+      <c r="B336" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C336" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D336" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E336" t="str">
+        <v>8</v>
+      </c>
+      <c r="F336" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G336" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H336" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I336" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J336" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K336" t="str">
+        <v/>
+      </c>
+      <c r="L336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>C2026.0336</v>
+      </c>
+      <c r="B337" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C337" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D337" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E337" t="str">
+        <v>8</v>
+      </c>
+      <c r="F337" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G337" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H337" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I337" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J337" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K337" t="str">
+        <v/>
+      </c>
+      <c r="L337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>C2026.0337</v>
+      </c>
+      <c r="B338" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C338" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D338" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E338" t="str">
+        <v>8</v>
+      </c>
+      <c r="F338" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G338" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H338" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I338" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J338" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K338" t="str">
+        <v/>
+      </c>
+      <c r="L338" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>C2026.0338</v>
+      </c>
+      <c r="B339" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C339" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D339" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E339" t="str">
+        <v>8</v>
+      </c>
+      <c r="F339" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G339" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H339" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I339" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J339" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K339" t="str">
+        <v/>
+      </c>
+      <c r="L339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>C2026.0339</v>
+      </c>
+      <c r="B340" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C340" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D340" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E340" t="str">
+        <v>8</v>
+      </c>
+      <c r="F340" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G340" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H340" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I340" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J340" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K340" t="str">
+        <v/>
+      </c>
+      <c r="L340" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>C2026.0340</v>
+      </c>
+      <c r="B341" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C341" t="str">
+        <v>52264013</v>
+      </c>
+      <c r="D341" t="str">
+        <v>BRACKET GEAR SHIFT MOUTING</v>
+      </c>
+      <c r="E341" t="str">
+        <v>8</v>
+      </c>
+      <c r="F341" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G341" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H341" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I341" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J341" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K341" t="str">
+        <v/>
+      </c>
+      <c r="L341" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>C2026.0341</v>
+      </c>
+      <c r="B342" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C342" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D342" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E342" t="str">
+        <v>8</v>
+      </c>
+      <c r="F342" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G342" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H342" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I342" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J342" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K342" t="str">
+        <v/>
+      </c>
+      <c r="L342" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>C2026.0342</v>
+      </c>
+      <c r="B343" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C343" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D343" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E343" t="str">
+        <v>8</v>
+      </c>
+      <c r="F343" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G343" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H343" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I343" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J343" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K343" t="str">
+        <v/>
+      </c>
+      <c r="L343" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>C2026.0343</v>
+      </c>
+      <c r="B344" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C344" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D344" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E344" t="str">
+        <v>8</v>
+      </c>
+      <c r="F344" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G344" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H344" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I344" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J344" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K344" t="str">
+        <v/>
+      </c>
+      <c r="L344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>C2026.0344</v>
+      </c>
+      <c r="B345" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C345" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D345" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E345" t="str">
+        <v>8</v>
+      </c>
+      <c r="F345" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G345" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H345" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I345" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J345" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K345" t="str">
+        <v/>
+      </c>
+      <c r="L345" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>C2026.0345</v>
+      </c>
+      <c r="B346" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C346" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D346" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E346" t="str">
+        <v>8</v>
+      </c>
+      <c r="F346" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G346" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H346" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I346" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J346" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K346" t="str">
+        <v/>
+      </c>
+      <c r="L346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>C2026.0346</v>
+      </c>
+      <c r="B347" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C347" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D347" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E347" t="str">
+        <v>8</v>
+      </c>
+      <c r="F347" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G347" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H347" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I347" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J347" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K347" t="str">
+        <v/>
+      </c>
+      <c r="L347" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>C2026.0347</v>
+      </c>
+      <c r="B348" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C348" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D348" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E348" t="str">
+        <v>8</v>
+      </c>
+      <c r="F348" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G348" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H348" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I348" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J348" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K348" t="str">
+        <v/>
+      </c>
+      <c r="L348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>C2026.0348</v>
+      </c>
+      <c r="B349" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C349" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D349" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E349" t="str">
+        <v>8</v>
+      </c>
+      <c r="F349" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G349" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H349" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I349" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J349" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K349" t="str">
+        <v/>
+      </c>
+      <c r="L349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>C2026.0349</v>
+      </c>
+      <c r="B350" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C350" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D350" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E350" t="str">
+        <v>8</v>
+      </c>
+      <c r="F350" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G350" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H350" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I350" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J350" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K350" t="str">
+        <v/>
+      </c>
+      <c r="L350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>C2026.0350</v>
+      </c>
+      <c r="B351" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C351" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D351" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E351" t="str">
+        <v>8</v>
+      </c>
+      <c r="F351" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G351" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H351" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I351" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J351" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K351" t="str">
+        <v/>
+      </c>
+      <c r="L351" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>C2026.0351</v>
+      </c>
+      <c r="B352" t="str">
+        <v>17/02/2026</v>
+      </c>
+      <c r="C352" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D352" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E352" t="str">
+        <v>8</v>
+      </c>
+      <c r="F352" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G352" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H352" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I352" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J352" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
+      <c r="L352" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>C2026.0352</v>
+      </c>
+      <c r="B353" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C353" t="str">
+        <v>53328133</v>
+      </c>
+      <c r="D353" t="str">
+        <v xml:space="preserve">STAFFA ATACCO PARAFANGO CENTR SX </v>
+      </c>
+      <c r="E353" t="str">
+        <v>8</v>
+      </c>
+      <c r="F353" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G353" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H353" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I353" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J353" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
+      <c r="L353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>C2026.0353</v>
+      </c>
+      <c r="B354" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C354" t="str">
+        <v>533281320</v>
+      </c>
+      <c r="D354" t="str">
+        <v>STAFFA ATACCO PARAFANGO CENTR DX</v>
+      </c>
+      <c r="E354" t="str">
+        <v>8</v>
+      </c>
+      <c r="F354" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G354" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H354" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I354" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J354" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
+      <c r="L354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" xml:space="preserve">
+      <c r="A355" t="str">
+        <v>C2026.0354</v>
+      </c>
+      <c r="B355" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C355" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D355" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E355" t="str">
+        <v>8</v>
+      </c>
+      <c r="F355" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G355" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H355" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I355" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J355" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K355" t="str" xml:space="preserve">
+        <v xml:space="preserve">PEÇAS EM DESVIO
+</v>
+      </c>
+      <c r="L355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" xml:space="preserve">
+      <c r="A356" t="str">
+        <v>C2026.0355</v>
+      </c>
+      <c r="B356" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C356" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D356" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E356" t="str">
+        <v>8</v>
+      </c>
+      <c r="F356" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G356" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H356" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I356" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J356" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K356" t="str" xml:space="preserve">
+        <v xml:space="preserve">PEÇAS EM DESVIO
+</v>
+      </c>
+      <c r="L356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>C2026.0356</v>
+      </c>
+      <c r="B357" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C357" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D357" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E357" t="str">
+        <v>8</v>
+      </c>
+      <c r="F357" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G357" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H357" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I357" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J357" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K357" t="str">
+        <v/>
+      </c>
+      <c r="L357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>C2026.0357</v>
+      </c>
+      <c r="B358" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C358" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D358" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E358" t="str">
+        <v>8</v>
+      </c>
+      <c r="F358" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G358" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H358" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I358" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J358" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K358" t="str">
+        <v/>
+      </c>
+      <c r="L358" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>C2026.0358</v>
+      </c>
+      <c r="B359" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C359" t="str">
+        <v>52264207</v>
+      </c>
+      <c r="D359" t="str">
+        <v xml:space="preserve">BRACKET BSG ELETRIC CABLE </v>
+      </c>
+      <c r="E359" t="str">
+        <v>8</v>
+      </c>
+      <c r="F359" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G359" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H359" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I359" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J359" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K359" t="str">
+        <v/>
+      </c>
+      <c r="L359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>C2026.0359</v>
+      </c>
+      <c r="B360" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C360" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D360" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E360" t="str">
+        <v>8</v>
+      </c>
+      <c r="F360" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G360" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H360" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I360" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J360" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K360" t="str">
+        <v/>
+      </c>
+      <c r="L360" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>C2026.0360</v>
+      </c>
+      <c r="B361" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C361" t="str">
+        <v>53489602</v>
+      </c>
+      <c r="D361" t="str">
+        <v>CURVÃO SX</v>
+      </c>
+      <c r="E361" t="str">
+        <v>8</v>
+      </c>
+      <c r="F361" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G361" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H361" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I361" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J361" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K361" t="str">
+        <v/>
+      </c>
+      <c r="L361" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>C2026.0361</v>
+      </c>
+      <c r="B362" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C362" t="str">
+        <v>53489539</v>
+      </c>
+      <c r="D362" t="str">
+        <v>CURVÃO DX</v>
+      </c>
+      <c r="E362" t="str">
+        <v>8</v>
+      </c>
+      <c r="F362" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G362" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H362" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I362" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J362" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K362" t="str">
+        <v/>
+      </c>
+      <c r="L362" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>C2026.0362</v>
+      </c>
+      <c r="B363" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C363" t="str">
+        <v>53489539</v>
+      </c>
+      <c r="D363" t="str">
+        <v>CURVÃO DX</v>
+      </c>
+      <c r="E363" t="str">
+        <v>8</v>
+      </c>
+      <c r="F363" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G363" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H363" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I363" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J363" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K363" t="str">
+        <v/>
+      </c>
+      <c r="L363" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>C2026.0363</v>
+      </c>
+      <c r="B364" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C364" t="str">
+        <v>53489539</v>
+      </c>
+      <c r="D364" t="str">
+        <v>CURVÃO DX</v>
+      </c>
+      <c r="E364" t="str">
+        <v>8</v>
+      </c>
+      <c r="F364" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G364" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H364" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I364" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J364" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K364" t="str">
+        <v/>
+      </c>
+      <c r="L364" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>C2026.0364</v>
+      </c>
+      <c r="B365" t="str">
+        <v>18/02/2026</v>
+      </c>
+      <c r="C365" t="str">
+        <v>52264207</v>
+      </c>
+      <c r="D365" t="str">
+        <v xml:space="preserve">BRACKET BSG ELETRIC CABLE </v>
+      </c>
+      <c r="E365" t="str">
+        <v>8</v>
+      </c>
+      <c r="F365" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G365" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H365" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I365" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J365" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K365" t="str">
+        <v/>
+      </c>
+      <c r="L365" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>C2026.0365</v>
+      </c>
+      <c r="B366" t="str">
+        <v>19/02/2026</v>
+      </c>
+      <c r="C366" t="str">
+        <v>534164540</v>
+      </c>
+      <c r="D366" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E366" t="str">
+        <v>8</v>
+      </c>
+      <c r="F366" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G366" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H366" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I366" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J366" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K366" t="str">
+        <v/>
+      </c>
+      <c r="L366" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>C2026.0366</v>
+      </c>
+      <c r="B367" t="str">
+        <v>19/02/2026</v>
+      </c>
+      <c r="C367" t="str">
+        <v>534164540</v>
+      </c>
+      <c r="D367" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA DX</v>
+      </c>
+      <c r="E367" t="str">
+        <v>7</v>
+      </c>
+      <c r="F367" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G367" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H367" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I367" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J367" t="str">
+        <v>LAMENTAÇÃO CLIENTE</v>
+      </c>
+      <c r="K367" t="str">
+        <v/>
+      </c>
+      <c r="L367" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>C2026.0367</v>
+      </c>
+      <c r="B368" t="str">
+        <v>20/02/2026</v>
+      </c>
+      <c r="C368" t="str">
+        <v>53376480</v>
+      </c>
+      <c r="D368" t="str">
+        <v>PONTEIRA DX</v>
+      </c>
+      <c r="E368" t="str">
+        <v>8</v>
+      </c>
+      <c r="F368" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G368" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H368" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I368" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J368" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K368" t="str">
+        <v/>
+      </c>
+      <c r="L368" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>C2026.0368</v>
+      </c>
+      <c r="B369" t="str">
+        <v>20/02/2026</v>
+      </c>
+      <c r="C369" t="str">
+        <v>52225420</v>
+      </c>
+      <c r="D369" t="str">
+        <v>PONTEIRA SX</v>
+      </c>
+      <c r="E369" t="str">
+        <v>8</v>
+      </c>
+      <c r="F369" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G369" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H369" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I369" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J369" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K369" t="str">
+        <v/>
+      </c>
+      <c r="L369" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>C2026.0369</v>
+      </c>
+      <c r="B370" t="str">
+        <v>20/02/2026</v>
+      </c>
+      <c r="C370" t="str">
+        <v>52225420</v>
+      </c>
+      <c r="D370" t="str">
+        <v>PONTEIRA SX</v>
+      </c>
+      <c r="E370" t="str">
+        <v>8</v>
+      </c>
+      <c r="F370" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G370" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H370" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I370" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J370" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K370" t="str">
+        <v/>
+      </c>
+      <c r="L370" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>C2026.0370</v>
+      </c>
+      <c r="B371" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C371" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D371" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E371" t="str">
+        <v>9</v>
+      </c>
+      <c r="F371" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G371" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H371" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I371" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J371" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K371" t="str">
+        <v/>
+      </c>
+      <c r="L371" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>C2026.0371</v>
+      </c>
+      <c r="B372" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C372" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D372" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E372" t="str">
+        <v>9</v>
+      </c>
+      <c r="F372" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G372" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H372" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I372" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J372" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K372" t="str">
+        <v/>
+      </c>
+      <c r="L372" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>C2026.0372</v>
+      </c>
+      <c r="B373" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C373" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D373" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E373" t="str">
+        <v>9</v>
+      </c>
+      <c r="F373" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G373" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H373" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I373" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J373" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K373" t="str">
+        <v/>
+      </c>
+      <c r="L373" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>C2026.0373</v>
+      </c>
+      <c r="B374" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C374" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D374" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E374" t="str">
+        <v>9</v>
+      </c>
+      <c r="F374" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G374" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H374" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I374" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J374" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K374" t="str">
+        <v/>
+      </c>
+      <c r="L374" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>C2026.0374</v>
+      </c>
+      <c r="B375" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C375" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D375" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E375" t="str">
+        <v>9</v>
+      </c>
+      <c r="F375" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G375" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H375" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I375" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J375" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K375" t="str">
+        <v/>
+      </c>
+      <c r="L375" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>C2026.0375</v>
+      </c>
+      <c r="B376" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C376" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D376" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E376" t="str">
+        <v>9</v>
+      </c>
+      <c r="F376" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G376" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H376" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I376" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J376" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K376" t="str">
+        <v/>
+      </c>
+      <c r="L376" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>C2026.0376</v>
+      </c>
+      <c r="B377" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C377" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D377" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E377" t="str">
+        <v>9</v>
+      </c>
+      <c r="F377" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G377" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H377" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I377" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J377" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K377" t="str">
+        <v/>
+      </c>
+      <c r="L377" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>C2026.0377</v>
+      </c>
+      <c r="B378" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C378" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D378" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E378" t="str">
+        <v>9</v>
+      </c>
+      <c r="F378" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G378" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H378" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I378" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J378" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K378" t="str">
+        <v/>
+      </c>
+      <c r="L378" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>C2026.0378</v>
+      </c>
+      <c r="B379" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C379" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D379" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E379" t="str">
+        <v>9</v>
+      </c>
+      <c r="F379" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G379" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H379" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I379" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J379" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K379" t="str">
+        <v/>
+      </c>
+      <c r="L379" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>C2026.0379</v>
+      </c>
+      <c r="B380" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C380" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D380" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E380" t="str">
+        <v>9</v>
+      </c>
+      <c r="F380" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G380" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H380" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I380" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J380" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K380" t="str">
+        <v/>
+      </c>
+      <c r="L380" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>C2026.0380</v>
+      </c>
+      <c r="B381" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C381" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D381" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E381" t="str">
+        <v>9</v>
+      </c>
+      <c r="F381" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G381" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H381" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I381" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J381" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
+      <c r="L381" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>C2026.0381</v>
+      </c>
+      <c r="B382" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C382" t="str">
+        <v>534895160</v>
+      </c>
+      <c r="D382" t="str">
+        <v>CALÇO SX</v>
+      </c>
+      <c r="E382" t="str">
+        <v>9</v>
+      </c>
+      <c r="F382" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G382" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H382" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I382" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J382" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
+      <c r="L382" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>C2026.0382</v>
+      </c>
+      <c r="B383" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C383" t="str">
+        <v>534895160</v>
+      </c>
+      <c r="D383" t="str">
+        <v>CALÇO SX</v>
+      </c>
+      <c r="E383" t="str">
+        <v>9</v>
+      </c>
+      <c r="F383" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G383" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H383" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I383" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J383" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
+      <c r="L383" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>C2026.0383</v>
+      </c>
+      <c r="B384" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C384" t="str">
+        <v>52259261</v>
+      </c>
+      <c r="D384" t="str">
+        <v>BRACKET 3-WAY VALVE</v>
+      </c>
+      <c r="E384" t="str">
+        <v>9</v>
+      </c>
+      <c r="F384" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G384" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H384" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I384" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J384" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K384" t="str">
+        <v/>
+      </c>
+      <c r="L384" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>C2026.0384</v>
+      </c>
+      <c r="B385" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C385" t="str">
+        <v>52259261</v>
+      </c>
+      <c r="D385" t="str">
+        <v>BRACKET 3-WAY VALVE</v>
+      </c>
+      <c r="E385" t="str">
+        <v>9</v>
+      </c>
+      <c r="F385" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G385" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H385" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I385" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J385" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K385" t="str">
+        <v/>
+      </c>
+      <c r="L385" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>C2026.0385</v>
+      </c>
+      <c r="B386" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C386" t="str">
+        <v>53489521</v>
+      </c>
+      <c r="D386" t="str">
+        <v>TRIDENTE DX</v>
+      </c>
+      <c r="E386" t="str">
+        <v>9</v>
+      </c>
+      <c r="F386" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G386" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H386" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I386" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J386" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K386" t="str">
+        <v/>
+      </c>
+      <c r="L386" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>C2026.0386</v>
+      </c>
+      <c r="B387" t="str">
+        <v>23/02/2026</v>
+      </c>
+      <c r="C387" t="str">
+        <v>53489521</v>
+      </c>
+      <c r="D387" t="str">
+        <v>TRIDENTE DX</v>
+      </c>
+      <c r="E387" t="str">
+        <v>9</v>
+      </c>
+      <c r="F387" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G387" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H387" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I387" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J387" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K387" t="str">
+        <v/>
+      </c>
+      <c r="L387" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>C2026.0387</v>
+      </c>
+      <c r="B388" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C388" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D388" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E388" t="str">
+        <v>9</v>
+      </c>
+      <c r="F388" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G388" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H388" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I388" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J388" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K388" t="str">
+        <v/>
+      </c>
+      <c r="L388" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>C2026.0388</v>
+      </c>
+      <c r="B389" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C389" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D389" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E389" t="str">
+        <v>9</v>
+      </c>
+      <c r="F389" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G389" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H389" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I389" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J389" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K389" t="str">
+        <v/>
+      </c>
+      <c r="L389" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>C2026.0389</v>
+      </c>
+      <c r="B390" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C390" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D390" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E390" t="str">
+        <v>9</v>
+      </c>
+      <c r="F390" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G390" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H390" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I390" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J390" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K390" t="str">
+        <v/>
+      </c>
+      <c r="L390" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>C2026.0390</v>
+      </c>
+      <c r="B391" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C391" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D391" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E391" t="str">
+        <v>9</v>
+      </c>
+      <c r="F391" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G391" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H391" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I391" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J391" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K391" t="str">
+        <v/>
+      </c>
+      <c r="L391" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>C2026.0391</v>
+      </c>
+      <c r="B392" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C392" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D392" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E392" t="str">
+        <v>9</v>
+      </c>
+      <c r="F392" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G392" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H392" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I392" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J392" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K392" t="str">
+        <v/>
+      </c>
+      <c r="L392" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>C2026.0392</v>
+      </c>
+      <c r="B393" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C393" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D393" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E393" t="str">
+        <v>9</v>
+      </c>
+      <c r="F393" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G393" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H393" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I393" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J393" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K393" t="str">
+        <v/>
+      </c>
+      <c r="L393" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>C2026.0393</v>
+      </c>
+      <c r="B394" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C394" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D394" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E394" t="str">
+        <v>9</v>
+      </c>
+      <c r="F394" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G394" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H394" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I394" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J394" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K394" t="str">
+        <v/>
+      </c>
+      <c r="L394" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>C2026.0394</v>
+      </c>
+      <c r="B395" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C395" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D395" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E395" t="str">
+        <v>9</v>
+      </c>
+      <c r="F395" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G395" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H395" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I395" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J395" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K395" t="str">
+        <v/>
+      </c>
+      <c r="L395" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>C2026.0395</v>
+      </c>
+      <c r="B396" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C396" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D396" t="str">
+        <v>TERMINAL DO SUPORTE DO TANQUE - POS3</v>
+      </c>
+      <c r="E396" t="str">
+        <v>9</v>
+      </c>
+      <c r="F396" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G396" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H396" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I396" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J396" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K396" t="str">
+        <v/>
+      </c>
+      <c r="L396" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>C2026.0396</v>
+      </c>
+      <c r="B397" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C397" t="str">
+        <v>521432790</v>
+      </c>
+      <c r="D397" t="str">
+        <v>SABONETEIRA 226</v>
+      </c>
+      <c r="E397" t="str">
+        <v>9</v>
+      </c>
+      <c r="F397" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G397" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H397" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I397" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J397" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K397" t="str">
+        <v/>
+      </c>
+      <c r="L397" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>C2026.0397</v>
+      </c>
+      <c r="B398" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C398" t="str">
+        <v>53489591</v>
+      </c>
+      <c r="D398" t="str">
+        <v>TRIDENTE SX</v>
+      </c>
+      <c r="E398" t="str">
+        <v>9</v>
+      </c>
+      <c r="F398" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G398" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H398" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I398" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J398" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K398" t="str">
+        <v/>
+      </c>
+      <c r="L398" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>C2026.0398</v>
+      </c>
+      <c r="B399" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C399" t="str">
+        <v>53489591</v>
+      </c>
+      <c r="D399" t="str">
+        <v>TRIDENTE SX</v>
+      </c>
+      <c r="E399" t="str">
+        <v>9</v>
+      </c>
+      <c r="F399" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G399" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H399" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I399" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J399" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K399" t="str">
+        <v/>
+      </c>
+      <c r="L399" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>C2026.0399</v>
+      </c>
+      <c r="B400" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C400" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D400" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E400" t="str">
+        <v>9</v>
+      </c>
+      <c r="F400" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G400" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H400" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I400" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J400" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K400" t="str">
+        <v/>
+      </c>
+      <c r="L400" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>C2026.0400</v>
+      </c>
+      <c r="B401" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C401" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D401" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E401" t="str">
+        <v>9</v>
+      </c>
+      <c r="F401" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G401" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H401" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I401" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J401" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K401" t="str">
+        <v/>
+      </c>
+      <c r="L401" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>C2026.0401</v>
+      </c>
+      <c r="B402" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C402" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D402" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E402" t="str">
+        <v>9</v>
+      </c>
+      <c r="F402" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G402" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H402" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I402" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J402" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K402" t="str">
+        <v/>
+      </c>
+      <c r="L402" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>C2026.0402</v>
+      </c>
+      <c r="B403" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C403" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D403" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E403" t="str">
+        <v>9</v>
+      </c>
+      <c r="F403" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G403" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H403" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I403" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J403" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K403" t="str">
+        <v/>
+      </c>
+      <c r="L403" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>C2026.0403</v>
+      </c>
+      <c r="B404" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C404" t="str">
+        <v>203086</v>
+      </c>
+      <c r="D404" t="str">
+        <v>ESPADA INOX MENOR DX</v>
+      </c>
+      <c r="E404" t="str">
+        <v>9</v>
+      </c>
+      <c r="F404" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G404" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H404" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I404" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J404" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K404" t="str">
+        <v>REPUXE</v>
+      </c>
+      <c r="L404" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>C2026.0404</v>
+      </c>
+      <c r="B405" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C405" t="str">
+        <v>203086</v>
+      </c>
+      <c r="D405" t="str">
+        <v>ESPADA INOX MENOR DX</v>
+      </c>
+      <c r="E405" t="str">
+        <v>9</v>
+      </c>
+      <c r="F405" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G405" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H405" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I405" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J405" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K405" t="str">
+        <v>REPUXE</v>
+      </c>
+      <c r="L405" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>C2026.0405</v>
+      </c>
+      <c r="B406" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C406" t="str">
+        <v>203087</v>
+      </c>
+      <c r="D406" t="str">
+        <v>ESPADA MENOR SX</v>
+      </c>
+      <c r="E406" t="str">
+        <v>9</v>
+      </c>
+      <c r="F406" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G406" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H406" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I406" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J406" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K406" t="str">
+        <v>REPUXE</v>
+      </c>
+      <c r="L406" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>C2026.0406</v>
+      </c>
+      <c r="B407" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C407" t="str">
+        <v>203087</v>
+      </c>
+      <c r="D407" t="str">
+        <v>ESPADA MENOR SX</v>
+      </c>
+      <c r="E407" t="str">
+        <v>9</v>
+      </c>
+      <c r="F407" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G407" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H407" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I407" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J407" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K407" t="str">
+        <v/>
+      </c>
+      <c r="L407" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>C2026.0407</v>
+      </c>
+      <c r="B408" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C408" t="str">
+        <v>FA00ACC91657</v>
+      </c>
+      <c r="D408" t="str">
+        <v>REINF PILLAR B</v>
+      </c>
+      <c r="E408" t="str">
+        <v>9</v>
+      </c>
+      <c r="F408" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G408" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H408" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I408" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J408" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K408" t="str">
+        <v/>
+      </c>
+      <c r="L408" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>C2026.0408</v>
+      </c>
+      <c r="B409" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C409" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D409" t="str">
+        <v>REIFORCEMENT TUBETO RT</v>
+      </c>
+      <c r="E409" t="str">
+        <v>9</v>
+      </c>
+      <c r="F409" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G409" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H409" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I409" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J409" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K409" t="str">
+        <v/>
+      </c>
+      <c r="L409" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>C2026.0409</v>
+      </c>
+      <c r="B410" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C410" t="str">
+        <v>53489520</v>
+      </c>
+      <c r="D410" t="str">
+        <v>REIFORCEMENT TUBETO LT</v>
+      </c>
+      <c r="E410" t="str">
+        <v>9</v>
+      </c>
+      <c r="F410" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G410" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H410" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I410" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J410" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K410" t="str">
+        <v/>
+      </c>
+      <c r="L410" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>C2026.0410</v>
+      </c>
+      <c r="B411" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C411" t="str">
+        <v>53490335</v>
+      </c>
+      <c r="D411" t="str">
+        <v>REIFORCEMENT TUBETO LT</v>
+      </c>
+      <c r="E411" t="str">
+        <v>9</v>
+      </c>
+      <c r="F411" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G411" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H411" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I411" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J411" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K411" t="str">
+        <v/>
+      </c>
+      <c r="L411" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>C2026.0411</v>
+      </c>
+      <c r="B412" t="str">
+        <v>24/02/2026</v>
+      </c>
+      <c r="C412" t="str">
+        <v>53490336</v>
+      </c>
+      <c r="D412" t="str">
+        <v>REIFORCEMENT TUBETO RT</v>
+      </c>
+      <c r="E412" t="str">
+        <v>9</v>
+      </c>
+      <c r="F412" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G412" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H412" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I412" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J412" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K412" t="str">
+        <v/>
+      </c>
+      <c r="L412" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>C2026.0412</v>
+      </c>
+      <c r="B413" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C413" t="str">
+        <v>53489540</v>
+      </c>
+      <c r="D413" t="str">
+        <v>CALÇO 02 DX</v>
+      </c>
+      <c r="E413" t="str">
+        <v>9</v>
+      </c>
+      <c r="F413" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G413" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H413" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I413" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J413" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K413" t="str">
+        <v/>
+      </c>
+      <c r="L413" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>C2026.0413</v>
+      </c>
+      <c r="B414" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C414" t="str">
+        <v>53489540</v>
+      </c>
+      <c r="D414" t="str">
+        <v>CALÇO 02 DX</v>
+      </c>
+      <c r="E414" t="str">
+        <v>9</v>
+      </c>
+      <c r="F414" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G414" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H414" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I414" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J414" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K414" t="str">
+        <v/>
+      </c>
+      <c r="L414" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>C2026.0414</v>
+      </c>
+      <c r="B415" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C415" t="str">
+        <v>53490336</v>
+      </c>
+      <c r="D415" t="str">
+        <v>CALÇO 01 DX</v>
+      </c>
+      <c r="E415" t="str">
+        <v>9</v>
+      </c>
+      <c r="F415" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G415" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H415" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I415" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J415" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K415" t="str">
+        <v/>
+      </c>
+      <c r="L415" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>C2026.0415</v>
+      </c>
+      <c r="B416" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C416" t="str">
+        <v>53489593</v>
+      </c>
+      <c r="D416" t="str">
+        <v>CALÇO 03 SX</v>
+      </c>
+      <c r="E416" t="str">
+        <v>9</v>
+      </c>
+      <c r="F416" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G416" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H416" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I416" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J416" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K416" t="str">
+        <v/>
+      </c>
+      <c r="L416" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>C2026.0416</v>
+      </c>
+      <c r="B417" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C417" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D417" t="str">
+        <v>saboneteira 226</v>
+      </c>
+      <c r="E417" t="str">
+        <v>9</v>
+      </c>
+      <c r="F417" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G417" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H417" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I417" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J417" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K417" t="str">
+        <v/>
+      </c>
+      <c r="L417" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>C2026.0417</v>
+      </c>
+      <c r="B418" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C418" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D418" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E418" t="str">
+        <v>9</v>
+      </c>
+      <c r="F418" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G418" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H418" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I418" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J418" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K418" t="str">
+        <v>PEÇA SINGELA</v>
+      </c>
+      <c r="L418" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>C2026.0418</v>
+      </c>
+      <c r="B419" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C419" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D419" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E419" t="str">
+        <v>9</v>
+      </c>
+      <c r="F419" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G419" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H419" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I419" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J419" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K419" t="str">
+        <v>PEÇA SINGELA</v>
+      </c>
+      <c r="L419" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>C2026.0419</v>
+      </c>
+      <c r="B420" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C420" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D420" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E420" t="str">
+        <v>9</v>
+      </c>
+      <c r="F420" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G420" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H420" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I420" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J420" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K420" t="str">
+        <v>PEÇA SINGELA</v>
+      </c>
+      <c r="L420" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>C2026.0420</v>
+      </c>
+      <c r="B421" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C421" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D421" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E421" t="str">
+        <v>9</v>
+      </c>
+      <c r="F421" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G421" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H421" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I421" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J421" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K421" t="str">
+        <v>PEÇA SINGELA</v>
+      </c>
+      <c r="L421" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>C2026.0421</v>
+      </c>
+      <c r="B422" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C422" t="str">
+        <v xml:space="preserve"> 52143278</v>
+      </c>
+      <c r="D422" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E422" t="str">
+        <v>9</v>
+      </c>
+      <c r="F422" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G422" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H422" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I422" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J422" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K422" t="str">
+        <v>PEÇA SINGELA</v>
+      </c>
+      <c r="L422" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>C2026.0422</v>
+      </c>
+      <c r="B423" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C423" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D423" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E423" t="str">
+        <v>9</v>
+      </c>
+      <c r="F423" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G423" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H423" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I423" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J423" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K423" t="str">
+        <v/>
+      </c>
+      <c r="L423" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>C2026.0423</v>
+      </c>
+      <c r="B424" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C424" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D424" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E424" t="str">
+        <v>9</v>
+      </c>
+      <c r="F424" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G424" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H424" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I424" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J424" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K424" t="str">
+        <v/>
+      </c>
+      <c r="L424" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>C2026.0424</v>
+      </c>
+      <c r="B425" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C425" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D425" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E425" t="str">
+        <v>9</v>
+      </c>
+      <c r="F425" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G425" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H425" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I425" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J425" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K425" t="str">
+        <v/>
+      </c>
+      <c r="L425" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>C2026.0425</v>
+      </c>
+      <c r="B426" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C426" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D426" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E426" t="str">
+        <v>9</v>
+      </c>
+      <c r="F426" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G426" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H426" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I426" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J426" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K426" t="str">
+        <v/>
+      </c>
+      <c r="L426" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>C2026.0426</v>
+      </c>
+      <c r="B427" t="str">
+        <v>25/02/2026</v>
+      </c>
+      <c r="C427" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D427" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E427" t="str">
+        <v>9</v>
+      </c>
+      <c r="F427" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G427" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H427" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I427" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J427" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K427" t="str">
+        <v/>
+      </c>
+      <c r="L427" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>C2026.0427</v>
+      </c>
+      <c r="B428" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C428" t="str">
+        <v>53489595</v>
+      </c>
+      <c r="D428" t="str">
+        <v>CALÇO 02 SX</v>
+      </c>
+      <c r="E428" t="str">
+        <v>9</v>
+      </c>
+      <c r="F428" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G428" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H428" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I428" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J428" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K428" t="str">
+        <v/>
+      </c>
+      <c r="L428" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>C2026.0428</v>
+      </c>
+      <c r="B429" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C429" t="str">
+        <v>53494973</v>
+      </c>
+      <c r="D429" t="str">
+        <v>PLACA DO SUPORTE DO TANQUE</v>
+      </c>
+      <c r="E429" t="str">
+        <v>9</v>
+      </c>
+      <c r="F429" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G429" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H429" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I429" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J429" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K429" t="str">
+        <v/>
+      </c>
+      <c r="L429" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>C2026.0429</v>
+      </c>
+      <c r="B430" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C430" t="str">
+        <v>53320775</v>
+      </c>
+      <c r="D430" t="str">
+        <v>REINF ASSY RR DOOR STRIKER RT</v>
+      </c>
+      <c r="E430" t="str">
+        <v>9</v>
+      </c>
+      <c r="F430" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G430" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H430" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I430" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J430" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K430" t="str">
+        <v/>
+      </c>
+      <c r="L430" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>C2026.0430</v>
+      </c>
+      <c r="B431" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C431" t="str">
+        <v>53320775</v>
+      </c>
+      <c r="D431" t="str">
+        <v>REINF ASSY RR DOOR STRIKER RT</v>
+      </c>
+      <c r="E431" t="str">
+        <v>9</v>
+      </c>
+      <c r="F431" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G431" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H431" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I431" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J431" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K431" t="str">
+        <v/>
+      </c>
+      <c r="L431" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>C2026.0431</v>
+      </c>
+      <c r="B432" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C432" t="str">
+        <v>53320775</v>
+      </c>
+      <c r="D432" t="str">
+        <v>REINF ASSY RR DOOR STRIKER RT</v>
+      </c>
+      <c r="E432" t="str">
+        <v>9</v>
+      </c>
+      <c r="F432" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G432" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H432" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I432" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J432" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K432" t="str">
+        <v/>
+      </c>
+      <c r="L432" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>C2026.0432</v>
+      </c>
+      <c r="B433" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C433" t="str">
+        <v>53320775</v>
+      </c>
+      <c r="D433" t="str">
+        <v>REINF ASSY RR DOOR STRIKER RT</v>
+      </c>
+      <c r="E433" t="str">
+        <v>9</v>
+      </c>
+      <c r="F433" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G433" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H433" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I433" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J433" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K433" t="str">
+        <v/>
+      </c>
+      <c r="L433" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>C2026.0433</v>
+      </c>
+      <c r="B434" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C434" t="str">
+        <v>53320775</v>
+      </c>
+      <c r="D434" t="str">
+        <v>REINF ASSY RR DOOR STRIKER RT</v>
+      </c>
+      <c r="E434" t="str">
+        <v>9</v>
+      </c>
+      <c r="F434" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G434" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H434" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I434" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J434" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K434" t="str">
+        <v/>
+      </c>
+      <c r="L434" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>C2026.0434</v>
+      </c>
+      <c r="B435" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C435" t="str">
+        <v>52162785</v>
+      </c>
+      <c r="D435" t="str">
+        <v>STAFFA POSTERIOR DX</v>
+      </c>
+      <c r="E435" t="str">
+        <v>9</v>
+      </c>
+      <c r="F435" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G435" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H435" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I435" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J435" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K435" t="str">
+        <v/>
+      </c>
+      <c r="L435" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>C2026.0435</v>
+      </c>
+      <c r="B436" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C436" t="str">
+        <v>52162785</v>
+      </c>
+      <c r="D436" t="str">
+        <v>STAFFA POSTERIOR DX</v>
+      </c>
+      <c r="E436" t="str">
+        <v>9</v>
+      </c>
+      <c r="F436" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G436" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H436" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I436" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J436" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K436" t="str">
+        <v/>
+      </c>
+      <c r="L436" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>C2026.0436</v>
+      </c>
+      <c r="B437" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C437" t="str">
+        <v>52162785</v>
+      </c>
+      <c r="D437" t="str">
+        <v>STAFFA POSTERIOR DX</v>
+      </c>
+      <c r="E437" t="str">
+        <v>9</v>
+      </c>
+      <c r="F437" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G437" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H437" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I437" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J437" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K437" t="str">
+        <v/>
+      </c>
+      <c r="L437" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>C2026.0437</v>
+      </c>
+      <c r="B438" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C438" t="str">
+        <v>52162785</v>
+      </c>
+      <c r="D438" t="str">
+        <v>STAFFA POSTERIOR DX</v>
+      </c>
+      <c r="E438" t="str">
+        <v>9</v>
+      </c>
+      <c r="F438" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G438" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H438" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I438" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J438" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K438" t="str">
+        <v/>
+      </c>
+      <c r="L438" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>C2026.0438</v>
+      </c>
+      <c r="B439" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C439" t="str">
+        <v>52162785</v>
+      </c>
+      <c r="D439" t="str">
+        <v>STAFFA POSTERIOR DX</v>
+      </c>
+      <c r="E439" t="str">
+        <v>9</v>
+      </c>
+      <c r="F439" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G439" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H439" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I439" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J439" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K439" t="str">
+        <v/>
+      </c>
+      <c r="L439" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>C2026.0439</v>
+      </c>
+      <c r="B440" t="str">
+        <v>26/02/2026</v>
+      </c>
+      <c r="C440" t="str">
+        <v>53328139</v>
+      </c>
+      <c r="D440" t="str">
+        <v>BRACKET ASSY FENDER MOUNTING FRT RT</v>
+      </c>
+      <c r="E440" t="str">
+        <v>9</v>
+      </c>
+      <c r="F440" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G440" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H440" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I440" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J440" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K440" t="str">
+        <v/>
+      </c>
+      <c r="L440" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>C2026.0440</v>
+      </c>
+      <c r="B441" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C441" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D441" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E441" t="str">
+        <v>9</v>
+      </c>
+      <c r="F441" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G441" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H441" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I441" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J441" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K441" t="str">
+        <v/>
+      </c>
+      <c r="L441" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>C2026.0441</v>
+      </c>
+      <c r="B442" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C442" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D442" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E442" t="str">
+        <v>9</v>
+      </c>
+      <c r="F442" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G442" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H442" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I442" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J442" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K442" t="str">
+        <v/>
+      </c>
+      <c r="L442" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>C2026.0442</v>
+      </c>
+      <c r="B443" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C443" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D443" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E443" t="str">
+        <v>9</v>
+      </c>
+      <c r="F443" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G443" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H443" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I443" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J443" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K443" t="str">
+        <v/>
+      </c>
+      <c r="L443" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>C2026.0443</v>
+      </c>
+      <c r="B444" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C444" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D444" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E444" t="str">
+        <v>9</v>
+      </c>
+      <c r="F444" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G444" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H444" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I444" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J444" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K444" t="str">
+        <v/>
+      </c>
+      <c r="L444" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>C2026.0444</v>
+      </c>
+      <c r="B445" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C445" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D445" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E445" t="str">
+        <v>9</v>
+      </c>
+      <c r="F445" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G445" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H445" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I445" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J445" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K445" t="str">
+        <v/>
+      </c>
+      <c r="L445" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>C2026.0445</v>
+      </c>
+      <c r="B446" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C446" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D446" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E446" t="str">
+        <v>9</v>
+      </c>
+      <c r="F446" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G446" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H446" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I446" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J446" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K446" t="str">
+        <v/>
+      </c>
+      <c r="L446" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>C2026.0446</v>
+      </c>
+      <c r="B447" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C447" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D447" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E447" t="str">
+        <v>9</v>
+      </c>
+      <c r="F447" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G447" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H447" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I447" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J447" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K447" t="str">
+        <v/>
+      </c>
+      <c r="L447" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>C2026.0447</v>
+      </c>
+      <c r="B448" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C448" t="str">
+        <v>52265834</v>
+      </c>
+      <c r="D448" t="str">
+        <v>BRACKET CASTELLO BATTERY</v>
+      </c>
+      <c r="E448" t="str">
+        <v>9</v>
+      </c>
+      <c r="F448" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G448" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H448" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I448" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J448" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K448" t="str">
+        <v/>
+      </c>
+      <c r="L448" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>C2026.0448</v>
+      </c>
+      <c r="B449" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C449" t="str">
+        <v>51947055</v>
+      </c>
+      <c r="D449" t="str">
+        <v>STAFFA COMPL FISS INF PARAFANGO LT</v>
+      </c>
+      <c r="E449" t="str">
+        <v>9</v>
+      </c>
+      <c r="F449" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G449" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H449" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I449" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J449" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K449" t="str">
+        <v/>
+      </c>
+      <c r="L449" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>C2026.0449</v>
+      </c>
+      <c r="B450" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C450" t="str">
+        <v>51947055</v>
+      </c>
+      <c r="D450" t="str">
+        <v>STAFFA COMPL FISS INF PARAFANGO LT</v>
+      </c>
+      <c r="E450" t="str">
+        <v>9</v>
+      </c>
+      <c r="F450" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G450" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H450" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I450" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J450" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K450" t="str">
+        <v/>
+      </c>
+      <c r="L450" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>C2026.0450</v>
+      </c>
+      <c r="B451" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C451" t="str">
+        <v>51947055</v>
+      </c>
+      <c r="D451" t="str">
+        <v>STAFFA COMPL FISS INF PARAFANGO LT</v>
+      </c>
+      <c r="E451" t="str">
+        <v>9</v>
+      </c>
+      <c r="F451" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G451" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H451" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I451" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J451" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K451" t="str">
+        <v/>
+      </c>
+      <c r="L451" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>C2026.0451</v>
+      </c>
+      <c r="B452" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C452" t="str">
+        <v>51947055</v>
+      </c>
+      <c r="D452" t="str">
+        <v>STAFFA COMPL FISS INF PARAFANGO LT</v>
+      </c>
+      <c r="E452" t="str">
+        <v>9</v>
+      </c>
+      <c r="F452" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G452" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H452" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I452" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J452" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K452" t="str">
+        <v/>
+      </c>
+      <c r="L452" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>C2026.0452</v>
+      </c>
+      <c r="B453" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C453" t="str">
+        <v>51947055</v>
+      </c>
+      <c r="D453" t="str">
+        <v>STAFFA COMPL FISS INF PARAFANGO LT</v>
+      </c>
+      <c r="E453" t="str">
+        <v>9</v>
+      </c>
+      <c r="F453" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G453" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H453" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I453" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J453" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K453" t="str">
+        <v/>
+      </c>
+      <c r="L453" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>C2026.0453</v>
+      </c>
+      <c r="B454" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C454" t="str">
+        <v>50167708</v>
+      </c>
+      <c r="D454" t="str">
+        <v>BRACKET UREA TANQUE</v>
+      </c>
+      <c r="E454" t="str">
+        <v>9</v>
+      </c>
+      <c r="F454" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G454" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H454" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I454" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J454" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K454" t="str">
+        <v/>
+      </c>
+      <c r="L454" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>C2026.0454</v>
+      </c>
+      <c r="B455" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C455" t="str">
+        <v>50167708</v>
+      </c>
+      <c r="D455" t="str">
+        <v>BRACKET UREA TANQUE</v>
+      </c>
+      <c r="E455" t="str">
+        <v>9</v>
+      </c>
+      <c r="F455" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G455" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H455" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I455" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J455" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K455" t="str">
+        <v/>
+      </c>
+      <c r="L455" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>C2026.0455</v>
+      </c>
+      <c r="B456" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C456" t="str">
+        <v>50167708</v>
+      </c>
+      <c r="D456" t="str">
+        <v>BRACKET UREA TANQUE</v>
+      </c>
+      <c r="E456" t="str">
+        <v>9</v>
+      </c>
+      <c r="F456" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G456" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H456" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I456" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J456" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K456" t="str">
+        <v/>
+      </c>
+      <c r="L456" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>C2026.0456</v>
+      </c>
+      <c r="B457" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C457" t="str">
+        <v>50167708</v>
+      </c>
+      <c r="D457" t="str">
+        <v>BRACKET UREA TANQUE</v>
+      </c>
+      <c r="E457" t="str">
+        <v>9</v>
+      </c>
+      <c r="F457" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G457" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H457" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I457" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J457" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K457" t="str">
+        <v/>
+      </c>
+      <c r="L457" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>C2026.0457</v>
+      </c>
+      <c r="B458" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C458" t="str">
+        <v>50167708</v>
+      </c>
+      <c r="D458" t="str">
+        <v>BRACKET UREA TANQUE</v>
+      </c>
+      <c r="E458" t="str">
+        <v>9</v>
+      </c>
+      <c r="F458" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G458" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H458" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I458" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J458" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K458" t="str">
+        <v/>
+      </c>
+      <c r="L458" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>C2026.0458</v>
+      </c>
+      <c r="B459" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C459" t="str">
+        <v>53346438</v>
+      </c>
+      <c r="D459" t="str">
+        <v>PUNTELLO PORTELLONE COMPL</v>
+      </c>
+      <c r="E459" t="str">
+        <v>9</v>
+      </c>
+      <c r="F459" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G459" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H459" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I459" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J459" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K459" t="str">
+        <v/>
+      </c>
+      <c r="L459" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>C2026.0459</v>
+      </c>
+      <c r="B460" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C460" t="str">
+        <v>53346438</v>
+      </c>
+      <c r="D460" t="str">
+        <v>PUNTELLO PORTELLONE COMPL</v>
+      </c>
+      <c r="E460" t="str">
+        <v>9</v>
+      </c>
+      <c r="F460" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G460" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H460" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I460" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J460" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K460" t="str">
+        <v/>
+      </c>
+      <c r="L460" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>C2026.0460</v>
+      </c>
+      <c r="B461" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C461" t="str">
+        <v>53346438</v>
+      </c>
+      <c r="D461" t="str">
+        <v>PUNTELLO PORTELLONE COMPL</v>
+      </c>
+      <c r="E461" t="str">
+        <v>9</v>
+      </c>
+      <c r="F461" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G461" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H461" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I461" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J461" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K461" t="str">
+        <v/>
+      </c>
+      <c r="L461" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>C2026.0461</v>
+      </c>
+      <c r="B462" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C462" t="str">
+        <v>53346438</v>
+      </c>
+      <c r="D462" t="str">
+        <v>PUNTELLO PORTELLONE COMPL</v>
+      </c>
+      <c r="E462" t="str">
+        <v>9</v>
+      </c>
+      <c r="F462" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G462" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H462" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I462" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J462" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K462" t="str">
+        <v/>
+      </c>
+      <c r="L462" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>C2026.0462</v>
+      </c>
+      <c r="B463" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C463" t="str">
+        <v>53346438</v>
+      </c>
+      <c r="D463" t="str">
+        <v>PUNTELLO PORTELLONE COMPL</v>
+      </c>
+      <c r="E463" t="str">
+        <v>9</v>
+      </c>
+      <c r="F463" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G463" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H463" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I463" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J463" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K463" t="str">
+        <v/>
+      </c>
+      <c r="L463" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>C2026.0463</v>
+      </c>
+      <c r="B464" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="C464" t="str">
+        <v>FA00ADG70842_POS02</v>
+      </c>
+      <c r="D464" t="str">
+        <v>TERMINAL SUPORT DO TANQUE</v>
+      </c>
+      <c r="E464" t="str">
+        <v>9</v>
+      </c>
+      <c r="F464" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G464" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H464" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I464" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J464" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K464" t="str">
+        <v/>
+      </c>
+      <c r="L464" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>C2026.0464</v>
+      </c>
+      <c r="B465" t="str">
+        <v>28/02/2026</v>
+      </c>
+      <c r="C465" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D465" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E465" t="str">
+        <v>9</v>
+      </c>
+      <c r="F465" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G465" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H465" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I465" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J465" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K465" t="str">
+        <v/>
+      </c>
+      <c r="L465" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>C2026.0465</v>
+      </c>
+      <c r="B466" t="str">
+        <v>28/02/2026</v>
+      </c>
+      <c r="C466" t="str">
+        <v>53416452</v>
+      </c>
+      <c r="D466" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E466" t="str">
+        <v>9</v>
+      </c>
+      <c r="F466" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G466" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H466" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I466" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J466" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K466" t="str">
+        <v/>
+      </c>
+      <c r="L466" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>C2026.0466</v>
+      </c>
+      <c r="B467" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C467" t="str">
+        <v>53490375</v>
+      </c>
+      <c r="D467" t="str">
+        <v>PEÇA DE LIGAÇÃO SX DO CHIFRINHO</v>
+      </c>
+      <c r="E467" t="str">
+        <v>10</v>
+      </c>
+      <c r="F467" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G467" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H467" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I467" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J467" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K467" t="str">
+        <v/>
+      </c>
+      <c r="L467" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>C2026.0467</v>
+      </c>
+      <c r="B468" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C468" t="str">
+        <v>53418337</v>
+      </c>
+      <c r="D468" t="str">
+        <v>BRACKET ASSY STAFFA CS LT</v>
+      </c>
+      <c r="E468" t="str">
+        <v>10</v>
+      </c>
+      <c r="F468" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G468" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H468" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I468" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J468" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K468" t="str">
+        <v/>
+      </c>
+      <c r="L468" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>C2026.0468</v>
+      </c>
+      <c r="B469" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C469" t="str">
+        <v>53418337</v>
+      </c>
+      <c r="D469" t="str">
+        <v>BRACKET ASSY STAFFA CS LT</v>
+      </c>
+      <c r="E469" t="str">
+        <v>10</v>
+      </c>
+      <c r="F469" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G469" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H469" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I469" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J469" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K469" t="str">
+        <v/>
+      </c>
+      <c r="L469" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>C2026.0469</v>
+      </c>
+      <c r="B470" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C470" t="str">
+        <v>53418337</v>
+      </c>
+      <c r="D470" t="str">
+        <v>BRACKET ASSY STAFFA CS LT</v>
+      </c>
+      <c r="E470" t="str">
+        <v>10</v>
+      </c>
+      <c r="F470" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G470" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H470" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I470" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J470" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K470" t="str">
+        <v/>
+      </c>
+      <c r="L470" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>C2026.0470</v>
+      </c>
+      <c r="B471" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C471" t="str">
+        <v>53418337</v>
+      </c>
+      <c r="D471" t="str">
+        <v>BRACKET ASSY STAFFA CS LT</v>
+      </c>
+      <c r="E471" t="str">
+        <v>10</v>
+      </c>
+      <c r="F471" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G471" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H471" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I471" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J471" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K471" t="str">
+        <v/>
+      </c>
+      <c r="L471" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>C2026.0471</v>
+      </c>
+      <c r="B472" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C472" t="str">
+        <v>53418337</v>
+      </c>
+      <c r="D472" t="str">
+        <v>BRACKET ASSY STAFFA CS LT</v>
+      </c>
+      <c r="E472" t="str">
+        <v>10</v>
+      </c>
+      <c r="F472" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G472" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H472" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I472" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J472" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K472" t="str">
+        <v/>
+      </c>
+      <c r="L472" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>C2026.0472</v>
+      </c>
+      <c r="B473" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C473" t="str">
+        <v>53418338</v>
+      </c>
+      <c r="D473" t="str">
+        <v>BRACKET ASSY  STAFFA CS RT</v>
+      </c>
+      <c r="E473" t="str">
+        <v>10</v>
+      </c>
+      <c r="F473" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G473" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H473" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I473" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J473" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K473" t="str">
+        <v/>
+      </c>
+      <c r="L473" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>C2026.0473</v>
+      </c>
+      <c r="B474" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C474" t="str">
+        <v>53418338</v>
+      </c>
+      <c r="D474" t="str">
+        <v>BRACKET ASSY  STAFFA CS RT</v>
+      </c>
+      <c r="E474" t="str">
+        <v>10</v>
+      </c>
+      <c r="F474" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G474" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H474" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I474" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J474" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K474" t="str">
+        <v/>
+      </c>
+      <c r="L474" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>C2026.0474</v>
+      </c>
+      <c r="B475" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C475" t="str">
+        <v>53418338</v>
+      </c>
+      <c r="D475" t="str">
+        <v>BRACKET ASSY  STAFFA CS RT</v>
+      </c>
+      <c r="E475" t="str">
+        <v>10</v>
+      </c>
+      <c r="F475" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G475" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H475" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I475" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J475" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K475" t="str">
+        <v/>
+      </c>
+      <c r="L475" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>C2026.0475</v>
+      </c>
+      <c r="B476" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C476" t="str">
+        <v>53418338</v>
+      </c>
+      <c r="D476" t="str">
+        <v>BRACKET ASSY  STAFFA CS RT</v>
+      </c>
+      <c r="E476" t="str">
+        <v>10</v>
+      </c>
+      <c r="F476" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G476" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H476" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I476" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J476" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K476" t="str">
+        <v/>
+      </c>
+      <c r="L476" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>C2026.0476</v>
+      </c>
+      <c r="B477" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C477" t="str">
+        <v>53418338</v>
+      </c>
+      <c r="D477" t="str">
+        <v>BRACKET ASSY  STAFFA CS RT</v>
+      </c>
+      <c r="E477" t="str">
+        <v>10</v>
+      </c>
+      <c r="F477" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G477" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H477" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I477" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J477" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K477" t="str">
+        <v/>
+      </c>
+      <c r="L477" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>C2026.0477</v>
+      </c>
+      <c r="B478" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C478" t="str">
+        <v>51988415</v>
+      </c>
+      <c r="D478" t="str">
+        <v>COVER RR RAIL RT</v>
+      </c>
+      <c r="E478" t="str">
+        <v>10</v>
+      </c>
+      <c r="F478" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G478" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H478" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I478" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J478" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K478" t="str">
+        <v/>
+      </c>
+      <c r="L478" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>C2026.0478</v>
+      </c>
+      <c r="B479" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C479" t="str">
+        <v>51988415</v>
+      </c>
+      <c r="D479" t="str">
+        <v>COVER RR RAIL RT</v>
+      </c>
+      <c r="E479" t="str">
+        <v>10</v>
+      </c>
+      <c r="F479" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G479" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H479" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I479" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J479" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K479" t="str">
+        <v/>
+      </c>
+      <c r="L479" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>C2026.0479</v>
+      </c>
+      <c r="B480" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C480" t="str">
+        <v>51988415</v>
+      </c>
+      <c r="D480" t="str">
+        <v>COVER RR RAIL RT</v>
+      </c>
+      <c r="E480" t="str">
+        <v>10</v>
+      </c>
+      <c r="F480" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G480" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H480" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I480" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J480" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K480" t="str">
+        <v/>
+      </c>
+      <c r="L480" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>C2026.0480</v>
+      </c>
+      <c r="B481" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C481" t="str">
+        <v>51988415</v>
+      </c>
+      <c r="D481" t="str">
+        <v>COVER RR RAIL RT</v>
+      </c>
+      <c r="E481" t="str">
+        <v>10</v>
+      </c>
+      <c r="F481" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G481" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H481" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I481" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J481" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K481" t="str">
+        <v/>
+      </c>
+      <c r="L481" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>C2026.0481</v>
+      </c>
+      <c r="B482" t="str">
+        <v>02/03/2026</v>
+      </c>
+      <c r="C482" t="str">
+        <v>51988415</v>
+      </c>
+      <c r="D482" t="str">
+        <v>COVER RR RAIL RT</v>
+      </c>
+      <c r="E482" t="str">
+        <v>10</v>
+      </c>
+      <c r="F482" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G482" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H482" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I482" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J482" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K482" t="str">
+        <v/>
+      </c>
+      <c r="L482" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>C2026.0482</v>
+      </c>
+      <c r="B483" t="str">
+        <v>03/03/2026</v>
+      </c>
+      <c r="C483" t="str">
+        <v>50165475</v>
+      </c>
+      <c r="D483" t="str">
+        <v>HOT FORM DX</v>
+      </c>
+      <c r="E483" t="str">
+        <v>10</v>
+      </c>
+      <c r="F483" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G483" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H483" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I483" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J483" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K483" t="str">
+        <v/>
+      </c>
+      <c r="L483" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>C2026.0483</v>
+      </c>
+      <c r="B484" t="str">
+        <v>03/03/2026</v>
+      </c>
+      <c r="C484" t="str">
+        <v>53490377</v>
+      </c>
+      <c r="D484" t="str">
+        <v>BARRA DE LIGAÇÇÇ]AO DX</v>
+      </c>
+      <c r="E484" t="str">
+        <v>10</v>
+      </c>
+      <c r="F484" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G484" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H484" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I484" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J484" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K484" t="str">
+        <v/>
+      </c>
+      <c r="L484" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L298"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L484"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/relatorios.xlsx
+++ b/data/relatorios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L770"/>
+  <dimension ref="A1:L861"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7081,7 +7081,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K176" t="str" xml:space="preserve">
-        <v xml:space="preserve">PREVENTIVA_x000d__x000d_
+        <v xml:space="preserve">PREVENTIVA_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L176" t="b">
@@ -7804,7 +7804,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K195" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d_
+        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L195" t="b">
@@ -13885,7 +13885,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K355" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L355" t="b">
@@ -13924,7 +13924,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K356" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L356" t="b">
@@ -18982,7 +18982,7 @@
         <v/>
       </c>
       <c r="L489" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -20692,7 +20692,7 @@
         <v/>
       </c>
       <c r="L534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -20730,7 +20730,7 @@
         <v/>
       </c>
       <c r="L535" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -21338,7 +21338,7 @@
         <v/>
       </c>
       <c r="L551" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="552">
@@ -21376,7 +21376,7 @@
         <v/>
       </c>
       <c r="L552" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="553">
@@ -21832,7 +21832,7 @@
         <v>TRY-OUT</v>
       </c>
       <c r="L564" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
@@ -21870,7 +21870,7 @@
         <v>TRY-OUT</v>
       </c>
       <c r="L565" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -21908,7 +21908,7 @@
         <v>TRY-OUT</v>
       </c>
       <c r="L566" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
@@ -22516,7 +22516,7 @@
         <v/>
       </c>
       <c r="L582" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583">
@@ -22554,7 +22554,7 @@
         <v/>
       </c>
       <c r="L583" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584">
@@ -23083,7 +23083,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K597" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L597" t="b">
@@ -23122,7 +23122,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K598" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d_
 </v>
       </c>
       <c r="L598" t="b">
@@ -23278,7 +23278,7 @@
         <v/>
       </c>
       <c r="L602" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
@@ -23316,7 +23316,7 @@
         <v/>
       </c>
       <c r="L603" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -24228,7 +24228,7 @@
         <v/>
       </c>
       <c r="L627" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="628">
@@ -24266,7 +24266,7 @@
         <v/>
       </c>
       <c r="L628" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="629">
@@ -24304,7 +24304,7 @@
         <v/>
       </c>
       <c r="L629" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="630">
@@ -24342,7 +24342,7 @@
         <v/>
       </c>
       <c r="L630" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631">
@@ -24380,7 +24380,7 @@
         <v/>
       </c>
       <c r="L631" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="632">
@@ -24532,7 +24532,7 @@
         <v/>
       </c>
       <c r="L635" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="636">
@@ -24570,7 +24570,7 @@
         <v/>
       </c>
       <c r="L636" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -24608,7 +24608,7 @@
         <v/>
       </c>
       <c r="L637" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="638">
@@ -24646,7 +24646,7 @@
         <v/>
       </c>
       <c r="L638" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
@@ -24684,7 +24684,7 @@
         <v/>
       </c>
       <c r="L639" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
@@ -24760,7 +24760,7 @@
         <v/>
       </c>
       <c r="L641" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642">
@@ -24798,7 +24798,7 @@
         <v/>
       </c>
       <c r="L642" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643">
@@ -24836,7 +24836,7 @@
         <v/>
       </c>
       <c r="L643" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -24874,7 +24874,7 @@
         <v/>
       </c>
       <c r="L644" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="645">
@@ -24912,7 +24912,7 @@
         <v/>
       </c>
       <c r="L645" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="646">
@@ -24988,7 +24988,7 @@
         <v/>
       </c>
       <c r="L647" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648">
@@ -25026,7 +25026,7 @@
         <v/>
       </c>
       <c r="L648" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
@@ -25064,7 +25064,7 @@
         <v/>
       </c>
       <c r="L649" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="650">
@@ -25102,7 +25102,7 @@
         <v/>
       </c>
       <c r="L650" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="651">
@@ -25140,7 +25140,7 @@
         <v>PRODUÇÃO 19/03/2026</v>
       </c>
       <c r="L651" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="652">
@@ -25368,7 +25368,7 @@
         <v/>
       </c>
       <c r="L657" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658">
@@ -25406,7 +25406,7 @@
         <v/>
       </c>
       <c r="L658" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659">
@@ -25444,7 +25444,7 @@
         <v/>
       </c>
       <c r="L659" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="660">
@@ -25482,7 +25482,7 @@
         <v/>
       </c>
       <c r="L660" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="661">
@@ -25520,7 +25520,7 @@
         <v/>
       </c>
       <c r="L661" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662">
@@ -25558,7 +25558,7 @@
         <v/>
       </c>
       <c r="L662" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663">
@@ -25596,7 +25596,7 @@
         <v/>
       </c>
       <c r="L663" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="664">
@@ -25634,7 +25634,7 @@
         <v/>
       </c>
       <c r="L664" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
@@ -25672,7 +25672,7 @@
         <v/>
       </c>
       <c r="L665" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
@@ -25710,7 +25710,7 @@
         <v/>
       </c>
       <c r="L666" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="667">
@@ -25748,7 +25748,7 @@
         <v/>
       </c>
       <c r="L667" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="668">
@@ -25786,7 +25786,7 @@
         <v/>
       </c>
       <c r="L668" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -25824,7 +25824,7 @@
         <v>TRY-OUT SEM GANHO.</v>
       </c>
       <c r="L669" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="670">
@@ -25862,7 +25862,7 @@
         <v>PRENSA PERDEU NITROGÊNIO.</v>
       </c>
       <c r="L670" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671">
@@ -25900,7 +25900,7 @@
         <v/>
       </c>
       <c r="L671" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="672">
@@ -29665,9 +29665,3467 @@
         <v>0</v>
       </c>
     </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>C2026.0770</v>
+      </c>
+      <c r="B771" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C771" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D771" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E771" t="str">
+        <v>13</v>
+      </c>
+      <c r="F771" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G771" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H771" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I771" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J771" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K771" t="str">
+        <v/>
+      </c>
+      <c r="L771" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>C2026.0771</v>
+      </c>
+      <c r="B772" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C772" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D772" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E772" t="str">
+        <v>13</v>
+      </c>
+      <c r="F772" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G772" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H772" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I772" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J772" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K772" t="str">
+        <v/>
+      </c>
+      <c r="L772" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>C2026.0772</v>
+      </c>
+      <c r="B773" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C773" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D773" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E773" t="str">
+        <v>13</v>
+      </c>
+      <c r="F773" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G773" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H773" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I773" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J773" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K773" t="str">
+        <v/>
+      </c>
+      <c r="L773" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>C2026.0773</v>
+      </c>
+      <c r="B774" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C774" t="str">
+        <v>53458377</v>
+      </c>
+      <c r="D774" t="str">
+        <v>BULKHEAD DX</v>
+      </c>
+      <c r="E774" t="str">
+        <v>13</v>
+      </c>
+      <c r="F774" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G774" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H774" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I774" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J774" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K774" t="str">
+        <v/>
+      </c>
+      <c r="L774" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>C2026.0774</v>
+      </c>
+      <c r="B775" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C775" t="str">
+        <v>53458377</v>
+      </c>
+      <c r="D775" t="str">
+        <v>BULKHEAD DX</v>
+      </c>
+      <c r="E775" t="str">
+        <v>13</v>
+      </c>
+      <c r="F775" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G775" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H775" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I775" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J775" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K775" t="str">
+        <v/>
+      </c>
+      <c r="L775" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>C2026.0775</v>
+      </c>
+      <c r="B776" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C776" t="str">
+        <v>53458377</v>
+      </c>
+      <c r="D776" t="str">
+        <v>BULKHEAD DX</v>
+      </c>
+      <c r="E776" t="str">
+        <v>13</v>
+      </c>
+      <c r="F776" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G776" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H776" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I776" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J776" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K776" t="str">
+        <v/>
+      </c>
+      <c r="L776" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>C2026.0776</v>
+      </c>
+      <c r="B777" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C777" t="str">
+        <v>53458377</v>
+      </c>
+      <c r="D777" t="str">
+        <v>BULKHEAD DX</v>
+      </c>
+      <c r="E777" t="str">
+        <v>13</v>
+      </c>
+      <c r="F777" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G777" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H777" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I777" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J777" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K777" t="str">
+        <v/>
+      </c>
+      <c r="L777" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>C2026.0777</v>
+      </c>
+      <c r="B778" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C778" t="str">
+        <v>53458377</v>
+      </c>
+      <c r="D778" t="str">
+        <v>BULKHEAD DX</v>
+      </c>
+      <c r="E778" t="str">
+        <v>13</v>
+      </c>
+      <c r="F778" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G778" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H778" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I778" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J778" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K778" t="str">
+        <v/>
+      </c>
+      <c r="L778" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>C2026.0778</v>
+      </c>
+      <c r="B779" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C779" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D779" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E779" t="str">
+        <v>13</v>
+      </c>
+      <c r="F779" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G779" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H779" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I779" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J779" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K779" t="str">
+        <v/>
+      </c>
+      <c r="L779" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>C2026.0779</v>
+      </c>
+      <c r="B780" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C780" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D780" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E780" t="str">
+        <v>13</v>
+      </c>
+      <c r="F780" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G780" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H780" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I780" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J780" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K780" t="str">
+        <v/>
+      </c>
+      <c r="L780" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>C2026.0780</v>
+      </c>
+      <c r="B781" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C781" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D781" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E781" t="str">
+        <v>13</v>
+      </c>
+      <c r="F781" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G781" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H781" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I781" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J781" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K781" t="str">
+        <v/>
+      </c>
+      <c r="L781" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>C2026.0781</v>
+      </c>
+      <c r="B782" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C782" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D782" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E782" t="str">
+        <v>13</v>
+      </c>
+      <c r="F782" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G782" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H782" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I782" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J782" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K782" t="str">
+        <v/>
+      </c>
+      <c r="L782" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>C2026.0782</v>
+      </c>
+      <c r="B783" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C783" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D783" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E783" t="str">
+        <v>13</v>
+      </c>
+      <c r="F783" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G783" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H783" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I783" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J783" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K783" t="str">
+        <v/>
+      </c>
+      <c r="L783" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>C2026.0783</v>
+      </c>
+      <c r="B784" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C784" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D784" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E784" t="str">
+        <v>13</v>
+      </c>
+      <c r="F784" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G784" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H784" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I784" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J784" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K784" t="str">
+        <v/>
+      </c>
+      <c r="L784" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>C2026.0784</v>
+      </c>
+      <c r="B785" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C785" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D785" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E785" t="str">
+        <v>13</v>
+      </c>
+      <c r="F785" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G785" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H785" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I785" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J785" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K785" t="str">
+        <v/>
+      </c>
+      <c r="L785" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>C2026.0785</v>
+      </c>
+      <c r="B786" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="C786" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D786" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E786" t="str">
+        <v>13</v>
+      </c>
+      <c r="F786" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G786" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H786" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I786" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J786" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K786" t="str">
+        <v/>
+      </c>
+      <c r="L786" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>C2026.0786</v>
+      </c>
+      <c r="B787" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C787" t="str">
+        <v>53490331</v>
+      </c>
+      <c r="D787" t="str">
+        <v>83.A - SAPATA DA LONGARINA DX</v>
+      </c>
+      <c r="E787" t="str">
+        <v>14</v>
+      </c>
+      <c r="F787" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G787" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H787" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I787" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J787" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K787" t="str">
+        <v/>
+      </c>
+      <c r="L787" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>C2026.0787</v>
+      </c>
+      <c r="B788" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C788" t="str">
+        <v>53490339</v>
+      </c>
+      <c r="D788" t="str">
+        <v>83.A - SAPATA DA LONGARINA SX</v>
+      </c>
+      <c r="E788" t="str">
+        <v>14</v>
+      </c>
+      <c r="F788" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G788" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H788" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I788" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J788" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K788" t="str">
+        <v/>
+      </c>
+      <c r="L788" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>C2026.0788</v>
+      </c>
+      <c r="B789" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C789" t="str">
+        <v>534894500</v>
+      </c>
+      <c r="D789" t="str">
+        <v>JOELHO DX</v>
+      </c>
+      <c r="E789" t="str">
+        <v>14</v>
+      </c>
+      <c r="F789" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G789" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H789" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I789" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J789" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K789" t="str">
+        <v/>
+      </c>
+      <c r="L789" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>C2026.0789</v>
+      </c>
+      <c r="B790" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C790" t="str">
+        <v>534947110</v>
+      </c>
+      <c r="D790" t="str">
+        <v>102.A - REDE GLOBO</v>
+      </c>
+      <c r="E790" t="str">
+        <v>14</v>
+      </c>
+      <c r="F790" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G790" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H790" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I790" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J790" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K790" t="str">
+        <v/>
+      </c>
+      <c r="L790" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>C2026.0790</v>
+      </c>
+      <c r="B791" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C791" t="str">
+        <v>533275360</v>
+      </c>
+      <c r="D791" t="str">
+        <v>62.A - SUPORTE DO TETO DX</v>
+      </c>
+      <c r="E791" t="str">
+        <v>14</v>
+      </c>
+      <c r="F791" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G791" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H791" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I791" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J791" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K791" t="str">
+        <v/>
+      </c>
+      <c r="L791" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>C2026.0791</v>
+      </c>
+      <c r="B792" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C792" t="str">
+        <v>534894530</v>
+      </c>
+      <c r="D792" t="str">
+        <v>JOELHO SX</v>
+      </c>
+      <c r="E792" t="str">
+        <v>14</v>
+      </c>
+      <c r="F792" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G792" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H792" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I792" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J792" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K792" t="str">
+        <v/>
+      </c>
+      <c r="L792" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>C2026.0792</v>
+      </c>
+      <c r="B793" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C793" t="str">
+        <v>53494973_POS.1</v>
+      </c>
+      <c r="D793" t="str">
+        <v xml:space="preserve">107.A - SUPORTE DO TANQUE CPL </v>
+      </c>
+      <c r="E793" t="str">
+        <v>14</v>
+      </c>
+      <c r="F793" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G793" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H793" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I793" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J793" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K793" t="str">
+        <v/>
+      </c>
+      <c r="L793" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>C2026.0793</v>
+      </c>
+      <c r="B794" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C794" t="str">
+        <v>51945497</v>
+      </c>
+      <c r="D794" t="str">
+        <v>MENSOLA SX</v>
+      </c>
+      <c r="E794" t="str">
+        <v>14</v>
+      </c>
+      <c r="F794" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G794" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H794" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I794" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J794" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K794" t="str">
+        <v/>
+      </c>
+      <c r="L794" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>C2026.0794</v>
+      </c>
+      <c r="B795" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C795" t="str">
+        <v>53490109</v>
+      </c>
+      <c r="D795" t="str">
+        <v>RINFORZO CS. PORTA POST. SX</v>
+      </c>
+      <c r="E795" t="str">
+        <v>14</v>
+      </c>
+      <c r="F795" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G795" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H795" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I795" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J795" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K795" t="str">
+        <v/>
+      </c>
+      <c r="L795" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>C2026.0795</v>
+      </c>
+      <c r="B796" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C796" t="str">
+        <v>53490109</v>
+      </c>
+      <c r="D796" t="str">
+        <v>RINFORZO CS. PORTA POST. SX</v>
+      </c>
+      <c r="E796" t="str">
+        <v>14</v>
+      </c>
+      <c r="F796" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G796" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H796" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I796" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J796" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K796" t="str">
+        <v/>
+      </c>
+      <c r="L796" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>C2026.0796</v>
+      </c>
+      <c r="B797" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C797" t="str">
+        <v>53490109</v>
+      </c>
+      <c r="D797" t="str">
+        <v>RINFORZO CS. PORTA POST. SX</v>
+      </c>
+      <c r="E797" t="str">
+        <v>14</v>
+      </c>
+      <c r="F797" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G797" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H797" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I797" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J797" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K797" t="str">
+        <v/>
+      </c>
+      <c r="L797" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>C2026.0797</v>
+      </c>
+      <c r="B798" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C798" t="str">
+        <v>53490109</v>
+      </c>
+      <c r="D798" t="str">
+        <v>RINFORZO CS. PORTA POST. SX</v>
+      </c>
+      <c r="E798" t="str">
+        <v>14</v>
+      </c>
+      <c r="F798" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G798" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H798" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I798" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J798" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K798" t="str">
+        <v/>
+      </c>
+      <c r="L798" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>C2026.0798</v>
+      </c>
+      <c r="B799" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C799" t="str">
+        <v>53490109</v>
+      </c>
+      <c r="D799" t="str">
+        <v>RINFORZO CS. PORTA POST. SX</v>
+      </c>
+      <c r="E799" t="str">
+        <v>14</v>
+      </c>
+      <c r="F799" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G799" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H799" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I799" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J799" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K799" t="str">
+        <v/>
+      </c>
+      <c r="L799" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>C2026.0799</v>
+      </c>
+      <c r="B800" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C800" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D800" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E800" t="str">
+        <v>14</v>
+      </c>
+      <c r="F800" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G800" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H800" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I800" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J800" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K800" t="str">
+        <v/>
+      </c>
+      <c r="L800" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>C2026.0800</v>
+      </c>
+      <c r="B801" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C801" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D801" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E801" t="str">
+        <v>14</v>
+      </c>
+      <c r="F801" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G801" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H801" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I801" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J801" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K801" t="str">
+        <v/>
+      </c>
+      <c r="L801" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>C2026.0801</v>
+      </c>
+      <c r="B802" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C802" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D802" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E802" t="str">
+        <v>14</v>
+      </c>
+      <c r="F802" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G802" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H802" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I802" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J802" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K802" t="str">
+        <v/>
+      </c>
+      <c r="L802" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>C2026.0802</v>
+      </c>
+      <c r="B803" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C803" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D803" t="str">
+        <v>RINFORZO COMPL. PORTA SX</v>
+      </c>
+      <c r="E803" t="str">
+        <v>14</v>
+      </c>
+      <c r="F803" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G803" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H803" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I803" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J803" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K803" t="str">
+        <v/>
+      </c>
+      <c r="L803" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>C2026.0803</v>
+      </c>
+      <c r="B804" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C804" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D804" t="str">
+        <v>RINFORZO COMPL. PORTA SX</v>
+      </c>
+      <c r="E804" t="str">
+        <v>14</v>
+      </c>
+      <c r="F804" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G804" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H804" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I804" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J804" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K804" t="str">
+        <v/>
+      </c>
+      <c r="L804" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>C2026.0804</v>
+      </c>
+      <c r="B805" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C805" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D805" t="str">
+        <v>RINFORZO COMPL. PORTA SX</v>
+      </c>
+      <c r="E805" t="str">
+        <v>14</v>
+      </c>
+      <c r="F805" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G805" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H805" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I805" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J805" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K805" t="str">
+        <v/>
+      </c>
+      <c r="L805" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>C2026.0805</v>
+      </c>
+      <c r="B806" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C806" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D806" t="str">
+        <v>RINFORZO COMPL. PORTA SX</v>
+      </c>
+      <c r="E806" t="str">
+        <v>14</v>
+      </c>
+      <c r="F806" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G806" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H806" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I806" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J806" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K806" t="str">
+        <v/>
+      </c>
+      <c r="L806" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>C2026.0806</v>
+      </c>
+      <c r="B807" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="C807" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D807" t="str">
+        <v>RINFORZO COMPL. PORTA SX</v>
+      </c>
+      <c r="E807" t="str">
+        <v>14</v>
+      </c>
+      <c r="F807" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G807" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H807" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I807" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J807" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K807" t="str">
+        <v/>
+      </c>
+      <c r="L807" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>C2026.0807</v>
+      </c>
+      <c r="B808" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C808" t="str">
+        <v>533785770</v>
+      </c>
+      <c r="D808" t="str">
+        <v>37.A - APOIO DA CINTA DO TANQUE DE COMBUSTIVEL</v>
+      </c>
+      <c r="E808" t="str">
+        <v>14</v>
+      </c>
+      <c r="F808" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G808" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H808" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I808" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J808" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K808" t="str">
+        <v/>
+      </c>
+      <c r="L808" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>C2026.0808</v>
+      </c>
+      <c r="B809" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C809" t="str">
+        <v>534895110</v>
+      </c>
+      <c r="D809" t="str">
+        <v>38.A - SUPORTE DO TANQUE DE COMBUSTIVEL</v>
+      </c>
+      <c r="E809" t="str">
+        <v>14</v>
+      </c>
+      <c r="F809" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G809" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H809" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I809" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J809" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K809" t="str">
+        <v/>
+      </c>
+      <c r="L809" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>C2026.0809</v>
+      </c>
+      <c r="B810" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C810" t="str">
+        <v>521627860</v>
+      </c>
+      <c r="D810" t="str">
+        <v>31.A - SUPORTE TRASEIRO SX</v>
+      </c>
+      <c r="E810" t="str">
+        <v>14</v>
+      </c>
+      <c r="F810" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G810" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H810" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I810" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J810" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K810" t="str">
+        <v/>
+      </c>
+      <c r="L810" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>C2026.0810</v>
+      </c>
+      <c r="B811" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C811" t="str">
+        <v>521627850</v>
+      </c>
+      <c r="D811" t="str">
+        <v>31.A - SUPORTE TRASEIRO DX</v>
+      </c>
+      <c r="E811" t="str">
+        <v>14</v>
+      </c>
+      <c r="F811" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G811" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H811" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I811" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J811" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K811" t="str">
+        <v/>
+      </c>
+      <c r="L811" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>C2026.0811</v>
+      </c>
+      <c r="B812" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C812" t="str">
+        <v>534897330</v>
+      </c>
+      <c r="D812" t="str">
+        <v>90.A - SUPORTE DO ARCO TRASEIRO</v>
+      </c>
+      <c r="E812" t="str">
+        <v>14</v>
+      </c>
+      <c r="F812" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G812" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H812" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I812" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J812" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K812" t="str">
+        <v/>
+      </c>
+      <c r="L812" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>C2026.0812</v>
+      </c>
+      <c r="B813" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C813" t="str">
+        <v>534943030</v>
+      </c>
+      <c r="D813" t="str">
+        <v>52.A - LAC340GI 1,50X299 SX</v>
+      </c>
+      <c r="E813" t="str">
+        <v>14</v>
+      </c>
+      <c r="F813" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G813" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H813" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I813" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J813" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K813" t="str">
+        <v/>
+      </c>
+      <c r="L813" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>C2026.0813</v>
+      </c>
+      <c r="B814" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C814" t="str">
+        <v>534943020</v>
+      </c>
+      <c r="D814" t="str">
+        <v>52.A - LAC340GI 1,50X299 DX</v>
+      </c>
+      <c r="E814" t="str">
+        <v>14</v>
+      </c>
+      <c r="F814" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G814" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H814" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I814" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J814" t="str">
+        <v>INSP DISPOSITIVO</v>
+      </c>
+      <c r="K814" t="str">
+        <v/>
+      </c>
+      <c r="L814" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>C2026.0814</v>
+      </c>
+      <c r="B815" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C815" t="str">
+        <v>52251530</v>
+      </c>
+      <c r="D815" t="str">
+        <v>BRACKET RR BRAKE HOSE RT</v>
+      </c>
+      <c r="E815" t="str">
+        <v>14</v>
+      </c>
+      <c r="F815" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G815" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H815" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I815" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J815" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K815" t="str">
+        <v/>
+      </c>
+      <c r="L815" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>C2026.0815</v>
+      </c>
+      <c r="B816" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C816" t="str">
+        <v>52251531</v>
+      </c>
+      <c r="D816" t="str">
+        <v>BRACKET RR BRAKE HOSE LT</v>
+      </c>
+      <c r="E816" t="str">
+        <v>14</v>
+      </c>
+      <c r="F816" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G816" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H816" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I816" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J816" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K816" t="str">
+        <v/>
+      </c>
+      <c r="L816" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>C2026.0816</v>
+      </c>
+      <c r="B817" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C817" t="str">
+        <v>53489514</v>
+      </c>
+      <c r="D817" t="str">
+        <v>CROSSMEMBER</v>
+      </c>
+      <c r="E817" t="str">
+        <v>14</v>
+      </c>
+      <c r="F817" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G817" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H817" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I817" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J817" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K817" t="str">
+        <v/>
+      </c>
+      <c r="L817" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>C2026.0817</v>
+      </c>
+      <c r="B818" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C818" t="str">
+        <v>53489519</v>
+      </c>
+      <c r="D818" t="str">
+        <v>TUBETO CROSS DX</v>
+      </c>
+      <c r="E818" t="str">
+        <v>14</v>
+      </c>
+      <c r="F818" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G818" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H818" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I818" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J818" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K818" t="str">
+        <v/>
+      </c>
+      <c r="L818" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>C2026.0818</v>
+      </c>
+      <c r="B819" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C819" t="str">
+        <v>53489514</v>
+      </c>
+      <c r="D819" t="str">
+        <v>CROSSMEMBER</v>
+      </c>
+      <c r="E819" t="str">
+        <v>14</v>
+      </c>
+      <c r="F819" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G819" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H819" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I819" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J819" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K819" t="str">
+        <v/>
+      </c>
+      <c r="L819" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>C2026.0819</v>
+      </c>
+      <c r="B820" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C820" t="str">
+        <v>53489514</v>
+      </c>
+      <c r="D820" t="str">
+        <v>CROSSMEMBER</v>
+      </c>
+      <c r="E820" t="str">
+        <v>14</v>
+      </c>
+      <c r="F820" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G820" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H820" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I820" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J820" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K820" t="str">
+        <v/>
+      </c>
+      <c r="L820" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
+        <v>C2026.0820</v>
+      </c>
+      <c r="B821" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C821" t="str">
+        <v>53489514</v>
+      </c>
+      <c r="D821" t="str">
+        <v>CROSSMEMBER</v>
+      </c>
+      <c r="E821" t="str">
+        <v>14</v>
+      </c>
+      <c r="F821" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G821" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H821" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I821" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J821" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K821" t="str">
+        <v/>
+      </c>
+      <c r="L821" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>C2026.0821</v>
+      </c>
+      <c r="B822" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C822" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D822" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA PORTA DX</v>
+      </c>
+      <c r="E822" t="str">
+        <v>14</v>
+      </c>
+      <c r="F822" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G822" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H822" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I822" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J822" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K822" t="str">
+        <v/>
+      </c>
+      <c r="L822" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>C2026.0822</v>
+      </c>
+      <c r="B823" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C823" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D823" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA PORTA DX</v>
+      </c>
+      <c r="E823" t="str">
+        <v>14</v>
+      </c>
+      <c r="F823" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G823" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H823" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I823" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J823" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K823" t="str">
+        <v/>
+      </c>
+      <c r="L823" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>C2026.0823</v>
+      </c>
+      <c r="B824" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C824" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D824" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA PORTA DX</v>
+      </c>
+      <c r="E824" t="str">
+        <v>14</v>
+      </c>
+      <c r="F824" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G824" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H824" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I824" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J824" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K824" t="str">
+        <v/>
+      </c>
+      <c r="L824" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>C2026.0824</v>
+      </c>
+      <c r="B825" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C825" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D825" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA PORTA DX</v>
+      </c>
+      <c r="E825" t="str">
+        <v>14</v>
+      </c>
+      <c r="F825" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G825" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H825" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I825" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J825" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K825" t="str">
+        <v/>
+      </c>
+      <c r="L825" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>C2026.0825</v>
+      </c>
+      <c r="B826" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C826" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D826" t="str">
+        <v>RINFORZO COMPL. MONT. CERNIERA PORTA DX</v>
+      </c>
+      <c r="E826" t="str">
+        <v>14</v>
+      </c>
+      <c r="F826" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G826" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H826" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I826" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J826" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K826" t="str">
+        <v/>
+      </c>
+      <c r="L826" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>C2026.0826</v>
+      </c>
+      <c r="B827" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C827" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D827" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E827" t="str">
+        <v>14</v>
+      </c>
+      <c r="F827" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G827" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H827" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I827" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J827" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K827" t="str">
+        <v/>
+      </c>
+      <c r="L827" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>C2026.0827</v>
+      </c>
+      <c r="B828" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C828" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D828" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E828" t="str">
+        <v>14</v>
+      </c>
+      <c r="F828" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G828" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H828" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I828" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J828" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K828" t="str">
+        <v/>
+      </c>
+      <c r="L828" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>C2026.0828</v>
+      </c>
+      <c r="B829" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C829" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D829" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E829" t="str">
+        <v>14</v>
+      </c>
+      <c r="F829" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G829" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H829" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I829" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J829" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K829" t="str">
+        <v/>
+      </c>
+      <c r="L829" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>C2026.0829</v>
+      </c>
+      <c r="B830" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C830" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D830" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E830" t="str">
+        <v>14</v>
+      </c>
+      <c r="F830" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G830" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H830" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I830" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J830" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K830" t="str">
+        <v/>
+      </c>
+      <c r="L830" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>C2026.0830</v>
+      </c>
+      <c r="B831" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="C831" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D831" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E831" t="str">
+        <v>14</v>
+      </c>
+      <c r="F831" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G831" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H831" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I831" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J831" t="str">
+        <v>TRYOUT</v>
+      </c>
+      <c r="K831" t="str">
+        <v/>
+      </c>
+      <c r="L831" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>C2026.0831</v>
+      </c>
+      <c r="B832" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C832" t="str">
+        <v>53489520</v>
+      </c>
+      <c r="D832" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E832" t="str">
+        <v>14</v>
+      </c>
+      <c r="F832" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G832" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H832" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I832" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J832" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K832" t="str">
+        <v/>
+      </c>
+      <c r="L832" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>C2026.0832</v>
+      </c>
+      <c r="B833" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C833" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D833" t="str">
+        <v>BRACKET BATTERY</v>
+      </c>
+      <c r="E833" t="str">
+        <v>14</v>
+      </c>
+      <c r="F833" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G833" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H833" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I833" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J833" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K833" t="str">
+        <v/>
+      </c>
+      <c r="L833" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>C2026.0833</v>
+      </c>
+      <c r="B834" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C834" t="str">
+        <v>53489520</v>
+      </c>
+      <c r="D834" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E834" t="str">
+        <v>14</v>
+      </c>
+      <c r="F834" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G834" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H834" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I834" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J834" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K834" t="str">
+        <v/>
+      </c>
+      <c r="L834" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>C2026.0834</v>
+      </c>
+      <c r="B835" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C835" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D835" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E835" t="str">
+        <v>14</v>
+      </c>
+      <c r="F835" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G835" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H835" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I835" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J835" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K835" t="str">
+        <v/>
+      </c>
+      <c r="L835" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>C2026.0835</v>
+      </c>
+      <c r="B836" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C836" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D836" t="str">
+        <v>LONGHERONE DX</v>
+      </c>
+      <c r="E836" t="str">
+        <v>14</v>
+      </c>
+      <c r="F836" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G836" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H836" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I836" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J836" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K836" t="str">
+        <v/>
+      </c>
+      <c r="L836" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>C2026.0836</v>
+      </c>
+      <c r="B837" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C837" t="str">
+        <v>52213242</v>
+      </c>
+      <c r="D837" t="str">
+        <v>BRACKET FENDER FRT RT</v>
+      </c>
+      <c r="E837" t="str">
+        <v>14</v>
+      </c>
+      <c r="F837" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G837" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H837" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I837" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J837" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K837" t="str">
+        <v/>
+      </c>
+      <c r="L837" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>C2026.0837</v>
+      </c>
+      <c r="B838" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C838" t="str">
+        <v>52213270</v>
+      </c>
+      <c r="D838" t="str">
+        <v>BRACKET FENDER FRT LT</v>
+      </c>
+      <c r="E838" t="str">
+        <v>14</v>
+      </c>
+      <c r="F838" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G838" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H838" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I838" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J838" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K838" t="str">
+        <v/>
+      </c>
+      <c r="L838" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>C2026.0838</v>
+      </c>
+      <c r="B839" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C839" t="str">
+        <v>53490093</v>
+      </c>
+      <c r="D839" t="str">
+        <v>REFORÇO DE FREIO SX</v>
+      </c>
+      <c r="E839" t="str">
+        <v>14</v>
+      </c>
+      <c r="F839" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G839" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H839" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I839" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J839" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K839" t="str">
+        <v/>
+      </c>
+      <c r="L839" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>C2026.0839</v>
+      </c>
+      <c r="B840" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C840" t="str">
+        <v>53490093</v>
+      </c>
+      <c r="D840" t="str">
+        <v>REFORÇO DE FREIO SX</v>
+      </c>
+      <c r="E840" t="str">
+        <v>14</v>
+      </c>
+      <c r="F840" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G840" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H840" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I840" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J840" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K840" t="str">
+        <v/>
+      </c>
+      <c r="L840" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>C2026.0840</v>
+      </c>
+      <c r="B841" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C841" t="str">
+        <v>53490093</v>
+      </c>
+      <c r="D841" t="str">
+        <v>REFORÇO DE FREIO SX</v>
+      </c>
+      <c r="E841" t="str">
+        <v>14</v>
+      </c>
+      <c r="F841" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G841" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H841" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I841" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J841" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K841" t="str">
+        <v/>
+      </c>
+      <c r="L841" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>C2026.0841</v>
+      </c>
+      <c r="B842" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C842" t="str">
+        <v>53490093</v>
+      </c>
+      <c r="D842" t="str">
+        <v>REFORÇO DE FREIO SX</v>
+      </c>
+      <c r="E842" t="str">
+        <v>14</v>
+      </c>
+      <c r="F842" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G842" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H842" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I842" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J842" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K842" t="str">
+        <v/>
+      </c>
+      <c r="L842" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>C2026.0842</v>
+      </c>
+      <c r="B843" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="C843" t="str">
+        <v>53490093</v>
+      </c>
+      <c r="D843" t="str">
+        <v>REFORÇO DE FREIO SX</v>
+      </c>
+      <c r="E843" t="str">
+        <v>14</v>
+      </c>
+      <c r="F843" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G843" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H843" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I843" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J843" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K843" t="str">
+        <v/>
+      </c>
+      <c r="L843" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>C2026.0843</v>
+      </c>
+      <c r="B844" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C844" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D844" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E844" t="str">
+        <v>14</v>
+      </c>
+      <c r="F844" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G844" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H844" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I844" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J844" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K844" t="str">
+        <v/>
+      </c>
+      <c r="L844" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>C2026.0844</v>
+      </c>
+      <c r="B845" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C845" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D845" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E845" t="str">
+        <v>14</v>
+      </c>
+      <c r="F845" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G845" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H845" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I845" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J845" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K845" t="str">
+        <v/>
+      </c>
+      <c r="L845" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>C2026.0845</v>
+      </c>
+      <c r="B846" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C846" t="str">
+        <v>53489593</v>
+      </c>
+      <c r="D846" t="str">
+        <v>CALÇO 03 SX</v>
+      </c>
+      <c r="E846" t="str">
+        <v>14</v>
+      </c>
+      <c r="F846" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G846" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H846" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I846" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J846" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K846" t="str">
+        <v/>
+      </c>
+      <c r="L846" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>C2026.0846</v>
+      </c>
+      <c r="B847" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C847" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D847" t="str">
+        <v>LONGHERONE SX</v>
+      </c>
+      <c r="E847" t="str">
+        <v>14</v>
+      </c>
+      <c r="F847" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G847" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H847" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I847" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J847" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K847" t="str">
+        <v/>
+      </c>
+      <c r="L847" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>C2026.0847</v>
+      </c>
+      <c r="B848" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C848" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D848" t="str">
+        <v>LONGHERONE SX</v>
+      </c>
+      <c r="E848" t="str">
+        <v>14</v>
+      </c>
+      <c r="F848" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G848" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H848" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I848" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J848" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K848" t="str">
+        <v/>
+      </c>
+      <c r="L848" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>C2026.0848</v>
+      </c>
+      <c r="B849" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C849" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D849" t="str">
+        <v>LONGHERONE SX</v>
+      </c>
+      <c r="E849" t="str">
+        <v>14</v>
+      </c>
+      <c r="F849" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G849" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H849" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I849" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J849" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K849" t="str">
+        <v/>
+      </c>
+      <c r="L849" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>C2026.0849</v>
+      </c>
+      <c r="B850" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C850" t="str">
+        <v>53493256</v>
+      </c>
+      <c r="D850" t="str">
+        <v>COPINHO</v>
+      </c>
+      <c r="E850" t="str">
+        <v>14</v>
+      </c>
+      <c r="F850" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G850" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H850" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I850" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J850" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K850" t="str">
+        <v/>
+      </c>
+      <c r="L850" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>C2026.0850</v>
+      </c>
+      <c r="B851" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C851" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D851" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E851" t="str">
+        <v>14</v>
+      </c>
+      <c r="F851" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G851" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H851" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I851" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J851" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K851" t="str">
+        <v/>
+      </c>
+      <c r="L851" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>C2026.0851</v>
+      </c>
+      <c r="B852" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C852" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D852" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E852" t="str">
+        <v>14</v>
+      </c>
+      <c r="F852" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G852" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H852" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I852" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J852" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K852" t="str">
+        <v/>
+      </c>
+      <c r="L852" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>C2026.0852</v>
+      </c>
+      <c r="B853" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C853" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D853" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E853" t="str">
+        <v>14</v>
+      </c>
+      <c r="F853" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G853" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H853" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I853" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J853" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K853" t="str">
+        <v/>
+      </c>
+      <c r="L853" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>C2026.0853</v>
+      </c>
+      <c r="B854" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C854" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D854" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E854" t="str">
+        <v>14</v>
+      </c>
+      <c r="F854" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G854" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H854" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I854" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J854" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K854" t="str">
+        <v/>
+      </c>
+      <c r="L854" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>C2026.0854</v>
+      </c>
+      <c r="B855" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C855" t="str">
+        <v>53490094</v>
+      </c>
+      <c r="D855" t="str">
+        <v>REFORÇO DE FREIO DX</v>
+      </c>
+      <c r="E855" t="str">
+        <v>14</v>
+      </c>
+      <c r="F855" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G855" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H855" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I855" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J855" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K855" t="str">
+        <v/>
+      </c>
+      <c r="L855" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>C2026.0855</v>
+      </c>
+      <c r="B856" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C856" t="str">
+        <v>53489572</v>
+      </c>
+      <c r="D856" t="str">
+        <v>LONGHERONE SX</v>
+      </c>
+      <c r="E856" t="str">
+        <v>14</v>
+      </c>
+      <c r="F856" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G856" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H856" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I856" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J856" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K856" t="str">
+        <v/>
+      </c>
+      <c r="L856" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>C2026.0856</v>
+      </c>
+      <c r="B857" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C857" t="str">
+        <v>100240605</v>
+      </c>
+      <c r="D857" t="str">
+        <v>PLACA DA SOLEIRA</v>
+      </c>
+      <c r="E857" t="str">
+        <v>14</v>
+      </c>
+      <c r="F857" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G857" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H857" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I857" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J857" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K857" t="str">
+        <v/>
+      </c>
+      <c r="L857" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>C2026.0857</v>
+      </c>
+      <c r="B858" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C858" t="str">
+        <v>100240605</v>
+      </c>
+      <c r="D858" t="str">
+        <v>PLACA DA SOLEIRA</v>
+      </c>
+      <c r="E858" t="str">
+        <v>14</v>
+      </c>
+      <c r="F858" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G858" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H858" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I858" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J858" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K858" t="str">
+        <v/>
+      </c>
+      <c r="L858" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v>C2026.0858</v>
+      </c>
+      <c r="B859" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C859" t="str">
+        <v>100240605</v>
+      </c>
+      <c r="D859" t="str">
+        <v>PLACA DA SOLEIRA</v>
+      </c>
+      <c r="E859" t="str">
+        <v>14</v>
+      </c>
+      <c r="F859" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G859" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H859" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I859" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J859" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K859" t="str">
+        <v/>
+      </c>
+      <c r="L859" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v>C2026.0859</v>
+      </c>
+      <c r="B860" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C860" t="str">
+        <v>100240605</v>
+      </c>
+      <c r="D860" t="str">
+        <v>PLACA DA SOLEIRA</v>
+      </c>
+      <c r="E860" t="str">
+        <v>14</v>
+      </c>
+      <c r="F860" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G860" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H860" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I860" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J860" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K860" t="str">
+        <v/>
+      </c>
+      <c r="L860" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v>C2026.0860</v>
+      </c>
+      <c r="B861" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="C861" t="str">
+        <v>100240605</v>
+      </c>
+      <c r="D861" t="str">
+        <v>PLACA DA SOLEIRA</v>
+      </c>
+      <c r="E861" t="str">
+        <v>14</v>
+      </c>
+      <c r="F861" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G861" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H861" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I861" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J861" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K861" t="str">
+        <v/>
+      </c>
+      <c r="L861" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L770"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L861"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/relatorios.xlsx
+++ b/data/relatorios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L861"/>
+  <dimension ref="A1:L935"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7081,7 +7081,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K176" t="str" xml:space="preserve">
-        <v xml:space="preserve">PREVENTIVA_x000d__x000d__x000d_
+        <v xml:space="preserve">PREVENTIVA_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L176" t="b">
@@ -7804,7 +7804,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K195" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L195" t="b">
@@ -13885,7 +13885,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K355" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L355" t="b">
@@ -13924,7 +13924,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K356" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L356" t="b">
@@ -23083,7 +23083,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K597" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L597" t="b">
@@ -23122,7 +23122,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K598" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L598" t="b">
@@ -33123,9 +33123,2821 @@
         <v>0</v>
       </c>
     </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v>C2026.0861</v>
+      </c>
+      <c r="B862" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C862" t="str">
+        <v>53377061</v>
+      </c>
+      <c r="D862" t="str">
+        <v>PRISMA</v>
+      </c>
+      <c r="E862" t="str">
+        <v>15</v>
+      </c>
+      <c r="F862" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G862" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H862" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I862" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J862" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K862" t="str">
+        <v/>
+      </c>
+      <c r="L862" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v>C2026.0862</v>
+      </c>
+      <c r="B863" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C863" t="str">
+        <v>53377061</v>
+      </c>
+      <c r="D863" t="str">
+        <v>PRISMA</v>
+      </c>
+      <c r="E863" t="str">
+        <v>15</v>
+      </c>
+      <c r="F863" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G863" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H863" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I863" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J863" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K863" t="str">
+        <v/>
+      </c>
+      <c r="L863" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v>C2026.0863</v>
+      </c>
+      <c r="B864" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C864" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D864" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E864" t="str">
+        <v>15</v>
+      </c>
+      <c r="F864" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G864" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H864" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I864" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J864" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K864" t="str">
+        <v/>
+      </c>
+      <c r="L864" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="str">
+        <v>C2026.0864</v>
+      </c>
+      <c r="B865" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C865" t="str">
+        <v>521432780</v>
+      </c>
+      <c r="D865" t="str">
+        <v>SERRATURA COFANO</v>
+      </c>
+      <c r="E865" t="str">
+        <v>15</v>
+      </c>
+      <c r="F865" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G865" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H865" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I865" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J865" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K865" t="str">
+        <v/>
+      </c>
+      <c r="L865" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v>C2026.0865</v>
+      </c>
+      <c r="B866" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C866" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D866" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E866" t="str">
+        <v>15</v>
+      </c>
+      <c r="F866" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G866" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H866" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I866" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J866" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K866" t="str">
+        <v/>
+      </c>
+      <c r="L866" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v>C2026.0866</v>
+      </c>
+      <c r="B867" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C867" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D867" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E867" t="str">
+        <v>15</v>
+      </c>
+      <c r="F867" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G867" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H867" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I867" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J867" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K867" t="str">
+        <v/>
+      </c>
+      <c r="L867" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>C2026.0867</v>
+      </c>
+      <c r="B868" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C868" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D868" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E868" t="str">
+        <v>15</v>
+      </c>
+      <c r="F868" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G868" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H868" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I868" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J868" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K868" t="str">
+        <v/>
+      </c>
+      <c r="L868" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="str">
+        <v>C2026.0868</v>
+      </c>
+      <c r="B869" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C869" t="str">
+        <v>53497979</v>
+      </c>
+      <c r="D869" t="str">
+        <v>SCONTRINO SERRATURA COFANO</v>
+      </c>
+      <c r="E869" t="str">
+        <v>15</v>
+      </c>
+      <c r="F869" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G869" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H869" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I869" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J869" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K869" t="str">
+        <v/>
+      </c>
+      <c r="L869" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="str">
+        <v>C2026.0869</v>
+      </c>
+      <c r="B870" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C870" t="str">
+        <v>53498105</v>
+      </c>
+      <c r="D870" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E870" t="str">
+        <v>15</v>
+      </c>
+      <c r="F870" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G870" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H870" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I870" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J870" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K870" t="str">
+        <v/>
+      </c>
+      <c r="L870" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="str">
+        <v>C2026.0870</v>
+      </c>
+      <c r="B871" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C871" t="str">
+        <v>53498106</v>
+      </c>
+      <c r="D871" t="str">
+        <v>CUCÃO SX</v>
+      </c>
+      <c r="E871" t="str">
+        <v>15</v>
+      </c>
+      <c r="F871" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G871" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H871" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I871" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J871" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K871" t="str">
+        <v/>
+      </c>
+      <c r="L871" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="str">
+        <v>C2026.0871</v>
+      </c>
+      <c r="B872" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C872" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D872" t="str">
+        <v>SERRATURA COFANO CPL</v>
+      </c>
+      <c r="E872" t="str">
+        <v>15</v>
+      </c>
+      <c r="F872" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G872" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H872" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I872" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J872" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K872" t="str">
+        <v/>
+      </c>
+      <c r="L872" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="str">
+        <v>C2026.0872</v>
+      </c>
+      <c r="B873" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C873" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D873" t="str">
+        <v>SERRATURA COFANO CPL</v>
+      </c>
+      <c r="E873" t="str">
+        <v>15</v>
+      </c>
+      <c r="F873" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G873" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H873" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I873" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J873" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K873" t="str">
+        <v/>
+      </c>
+      <c r="L873" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="str">
+        <v>C2026.0873</v>
+      </c>
+      <c r="B874" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C874" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D874" t="str">
+        <v>SERRATURA COFANO CPL</v>
+      </c>
+      <c r="E874" t="str">
+        <v>15</v>
+      </c>
+      <c r="F874" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G874" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H874" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I874" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J874" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K874" t="str">
+        <v/>
+      </c>
+      <c r="L874" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="str">
+        <v>C2026.0874</v>
+      </c>
+      <c r="B875" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C875" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D875" t="str">
+        <v>SERRATURA COFANO CPL</v>
+      </c>
+      <c r="E875" t="str">
+        <v>15</v>
+      </c>
+      <c r="F875" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G875" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H875" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I875" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J875" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K875" t="str">
+        <v/>
+      </c>
+      <c r="L875" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="str">
+        <v>C2026.0875</v>
+      </c>
+      <c r="B876" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C876" t="str">
+        <v>52143278</v>
+      </c>
+      <c r="D876" t="str">
+        <v>SERRATURA COFANO CPL</v>
+      </c>
+      <c r="E876" t="str">
+        <v>15</v>
+      </c>
+      <c r="F876" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G876" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H876" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I876" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J876" t="str">
+        <v>PPAP</v>
+      </c>
+      <c r="K876" t="str">
+        <v/>
+      </c>
+      <c r="L876" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="str">
+        <v>C2026.0876</v>
+      </c>
+      <c r="B877" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C877" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D877" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E877" t="str">
+        <v>15</v>
+      </c>
+      <c r="F877" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G877" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H877" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I877" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J877" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K877" t="str">
+        <v/>
+      </c>
+      <c r="L877" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="str">
+        <v>C2026.0877</v>
+      </c>
+      <c r="B878" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C878" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D878" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E878" t="str">
+        <v>15</v>
+      </c>
+      <c r="F878" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G878" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H878" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I878" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J878" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K878" t="str">
+        <v/>
+      </c>
+      <c r="L878" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="str">
+        <v>C2026.0878</v>
+      </c>
+      <c r="B879" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C879" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D879" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E879" t="str">
+        <v>15</v>
+      </c>
+      <c r="F879" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G879" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H879" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I879" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J879" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K879" t="str">
+        <v/>
+      </c>
+      <c r="L879" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="str">
+        <v>C2026.0879</v>
+      </c>
+      <c r="B880" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C880" t="str">
+        <v>51966401</v>
+      </c>
+      <c r="D880" t="str">
+        <v>SIDE BAR SUPPORTO DI SCORTA</v>
+      </c>
+      <c r="E880" t="str">
+        <v>15</v>
+      </c>
+      <c r="F880" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G880" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H880" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I880" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J880" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K880" t="str">
+        <v>PRODUÇÃO 06/04/2026</v>
+      </c>
+      <c r="L880" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="str">
+        <v>C2026.0880</v>
+      </c>
+      <c r="B881" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C881" t="str">
+        <v>51966402</v>
+      </c>
+      <c r="D881" t="str">
+        <v>SIDE BAR SUPPORTO DI SCORTA</v>
+      </c>
+      <c r="E881" t="str">
+        <v>15</v>
+      </c>
+      <c r="F881" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G881" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H881" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I881" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J881" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K881" t="str">
+        <v>PRODUÇÃO 06/04/2027</v>
+      </c>
+      <c r="L881" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="str">
+        <v>C2026.0881</v>
+      </c>
+      <c r="B882" t="str">
+        <v>06/04/2026</v>
+      </c>
+      <c r="C882" t="str">
+        <v>51966400</v>
+      </c>
+      <c r="D882" t="str">
+        <v>BRACKET CENTRAL CS</v>
+      </c>
+      <c r="E882" t="str">
+        <v>15</v>
+      </c>
+      <c r="F882" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G882" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H882" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I882" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J882" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K882" t="str">
+        <v/>
+      </c>
+      <c r="L882" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="str">
+        <v>C2026.0882</v>
+      </c>
+      <c r="B883" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C883" t="str">
+        <v>53416452</v>
+      </c>
+      <c r="D883" t="str">
+        <v>CUCÃO DX</v>
+      </c>
+      <c r="E883" t="str">
+        <v>15</v>
+      </c>
+      <c r="F883" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G883" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H883" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I883" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J883" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K883" t="str">
+        <v/>
+      </c>
+      <c r="L883" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="str">
+        <v>C2026.0883</v>
+      </c>
+      <c r="B884" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C884" t="str">
+        <v>53416453</v>
+      </c>
+      <c r="D884" t="str">
+        <v>CUCÃO SX</v>
+      </c>
+      <c r="E884" t="str">
+        <v>15</v>
+      </c>
+      <c r="F884" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G884" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H884" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I884" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J884" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K884" t="str">
+        <v/>
+      </c>
+      <c r="L884" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="str">
+        <v>C2026.0884</v>
+      </c>
+      <c r="B885" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C885" t="str">
+        <v>53490364</v>
+      </c>
+      <c r="D885" t="str">
+        <v>BRACKET COMPL. SX</v>
+      </c>
+      <c r="E885" t="str">
+        <v>15</v>
+      </c>
+      <c r="F885" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G885" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H885" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I885" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J885" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K885" t="str">
+        <v/>
+      </c>
+      <c r="L885" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="str">
+        <v>C2026.0885</v>
+      </c>
+      <c r="B886" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C886" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D886" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E886" t="str">
+        <v>15</v>
+      </c>
+      <c r="F886" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G886" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H886" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I886" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J886" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K886" t="str">
+        <v/>
+      </c>
+      <c r="L886" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="str">
+        <v>C2026.0886</v>
+      </c>
+      <c r="B887" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C887" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D887" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E887" t="str">
+        <v>15</v>
+      </c>
+      <c r="F887" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G887" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H887" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I887" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J887" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K887" t="str">
+        <v/>
+      </c>
+      <c r="L887" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="str">
+        <v>C2026.0887</v>
+      </c>
+      <c r="B888" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C888" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D888" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E888" t="str">
+        <v>15</v>
+      </c>
+      <c r="F888" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G888" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H888" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I888" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J888" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K888" t="str">
+        <v/>
+      </c>
+      <c r="L888" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="str">
+        <v>C2026.0888</v>
+      </c>
+      <c r="B889" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C889" t="str">
+        <v>53490309</v>
+      </c>
+      <c r="D889" t="str">
+        <v>BRACKET COMPL. DX</v>
+      </c>
+      <c r="E889" t="str">
+        <v>15</v>
+      </c>
+      <c r="F889" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G889" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H889" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I889" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J889" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K889" t="str">
+        <v/>
+      </c>
+      <c r="L889" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="str">
+        <v>C2026.0889</v>
+      </c>
+      <c r="B890" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C890" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D890" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E890" t="str">
+        <v>15</v>
+      </c>
+      <c r="F890" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G890" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H890" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I890" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J890" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K890" t="str">
+        <v/>
+      </c>
+      <c r="L890" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="str">
+        <v>C2026.0890</v>
+      </c>
+      <c r="B891" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C891" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D891" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E891" t="str">
+        <v>15</v>
+      </c>
+      <c r="F891" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G891" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H891" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I891" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J891" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K891" t="str">
+        <v/>
+      </c>
+      <c r="L891" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="str">
+        <v>C2026.0891</v>
+      </c>
+      <c r="B892" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C892" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D892" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E892" t="str">
+        <v>15</v>
+      </c>
+      <c r="F892" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G892" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H892" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I892" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J892" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K892" t="str">
+        <v/>
+      </c>
+      <c r="L892" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="str">
+        <v>C2026.0892</v>
+      </c>
+      <c r="B893" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C893" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D893" t="str">
+        <v>RACKET ASSY F. M. FRT LT</v>
+      </c>
+      <c r="E893" t="str">
+        <v>15</v>
+      </c>
+      <c r="F893" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G893" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H893" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I893" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J893" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K893" t="str">
+        <v/>
+      </c>
+      <c r="L893" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="str">
+        <v>C2026.0893</v>
+      </c>
+      <c r="B894" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C894" t="str">
+        <v>53328139</v>
+      </c>
+      <c r="D894" t="str">
+        <v>BRACKET ASSY FENDER MOUNTING FRT RT</v>
+      </c>
+      <c r="E894" t="str">
+        <v>15</v>
+      </c>
+      <c r="F894" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G894" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H894" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I894" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J894" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K894" t="str">
+        <v/>
+      </c>
+      <c r="L894" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="str">
+        <v>C2026.0894</v>
+      </c>
+      <c r="B895" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="C895" t="str">
+        <v>53489451</v>
+      </c>
+      <c r="D895" t="str">
+        <v>SIDE SILL SX</v>
+      </c>
+      <c r="E895" t="str">
+        <v>15</v>
+      </c>
+      <c r="F895" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G895" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H895" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I895" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J895" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K895" t="str">
+        <v/>
+      </c>
+      <c r="L895" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="str">
+        <v>C2026.0895</v>
+      </c>
+      <c r="B896" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C896" t="str">
+        <v>53327241</v>
+      </c>
+      <c r="D896" t="str">
+        <v>MÃO FRANCESA</v>
+      </c>
+      <c r="E896" t="str">
+        <v>15</v>
+      </c>
+      <c r="F896" t="str">
+        <v>ENGENHARIA</v>
+      </c>
+      <c r="G896" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H896" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I896" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J896" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K896" t="str">
+        <v/>
+      </c>
+      <c r="L896" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="str">
+        <v>C2026.0896</v>
+      </c>
+      <c r="B897" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C897" t="str">
+        <v>53328139</v>
+      </c>
+      <c r="D897" t="str">
+        <v>TORRESMO DX</v>
+      </c>
+      <c r="E897" t="str">
+        <v>15</v>
+      </c>
+      <c r="F897" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G897" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H897" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I897" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J897" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K897" t="str">
+        <v/>
+      </c>
+      <c r="L897" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="str">
+        <v>C2026.0897</v>
+      </c>
+      <c r="B898" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C898" t="str">
+        <v>53327786</v>
+      </c>
+      <c r="D898" t="str">
+        <v>bendita dx</v>
+      </c>
+      <c r="E898" t="str">
+        <v>15</v>
+      </c>
+      <c r="F898" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G898" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H898" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I898" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J898" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K898" t="str">
+        <v/>
+      </c>
+      <c r="L898" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="str">
+        <v>C2026.0898</v>
+      </c>
+      <c r="B899" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C899" t="str">
+        <v>53327797</v>
+      </c>
+      <c r="D899" t="str">
+        <v>BENDITA SX</v>
+      </c>
+      <c r="E899" t="str">
+        <v>15</v>
+      </c>
+      <c r="F899" t="str">
+        <v>FERRAMENTARIA</v>
+      </c>
+      <c r="G899" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H899" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I899" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J899" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K899" t="str">
+        <v/>
+      </c>
+      <c r="L899" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="str">
+        <v>C2026.0899</v>
+      </c>
+      <c r="B900" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C900" t="str">
+        <v>53328140</v>
+      </c>
+      <c r="D900" t="str">
+        <v>TORRESMO SX</v>
+      </c>
+      <c r="E900" t="str">
+        <v>15</v>
+      </c>
+      <c r="F900" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G900" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H900" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I900" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J900" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K900" t="str">
+        <v/>
+      </c>
+      <c r="L900" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="str">
+        <v>C2026.0900</v>
+      </c>
+      <c r="B901" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C901" t="str">
+        <v>53377061</v>
+      </c>
+      <c r="D901" t="str">
+        <v>PRISMA</v>
+      </c>
+      <c r="E901" t="str">
+        <v>15</v>
+      </c>
+      <c r="F901" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G901" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H901" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I901" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J901" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K901" t="str">
+        <v/>
+      </c>
+      <c r="L901" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="str">
+        <v>C2026.0901</v>
+      </c>
+      <c r="B902" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C902" t="str">
+        <v>53377061</v>
+      </c>
+      <c r="D902" t="str">
+        <v>RINFORZO SERRATURA PORTELLONE</v>
+      </c>
+      <c r="E902" t="str">
+        <v>15</v>
+      </c>
+      <c r="F902" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G902" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H902" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I902" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J902" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K902" t="str">
+        <v/>
+      </c>
+      <c r="L902" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="str">
+        <v>C2026.0902</v>
+      </c>
+      <c r="B903" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C903" t="str">
+        <v>53327797</v>
+      </c>
+      <c r="D903" t="str">
+        <v>SUPPORTO CS. MODULO FRONT END SX</v>
+      </c>
+      <c r="E903" t="str">
+        <v>15</v>
+      </c>
+      <c r="F903" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G903" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H903" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I903" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J903" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K903" t="str">
+        <v/>
+      </c>
+      <c r="L903" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="str">
+        <v>C2026.0903</v>
+      </c>
+      <c r="B904" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C904" t="str">
+        <v>53327786</v>
+      </c>
+      <c r="D904" t="str">
+        <v>SUPPORTO CS. MODULO FRONT END DX</v>
+      </c>
+      <c r="E904" t="str">
+        <v>15</v>
+      </c>
+      <c r="F904" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G904" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H904" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I904" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J904" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K904" t="str">
+        <v/>
+      </c>
+      <c r="L904" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="str">
+        <v>C2026.0904</v>
+      </c>
+      <c r="B905" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C905" t="str">
+        <v>53327786</v>
+      </c>
+      <c r="D905" t="str">
+        <v>SUPPORTO CS. MODULO FRONT END DX</v>
+      </c>
+      <c r="E905" t="str">
+        <v>15</v>
+      </c>
+      <c r="F905" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G905" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H905" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I905" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J905" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K905" t="str">
+        <v/>
+      </c>
+      <c r="L905" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="str">
+        <v>C2026.0905</v>
+      </c>
+      <c r="B906" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C906" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D906" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E906" t="str">
+        <v>15</v>
+      </c>
+      <c r="F906" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G906" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H906" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I906" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J906" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K906" t="str">
+        <v/>
+      </c>
+      <c r="L906" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="str">
+        <v>C2026.0906</v>
+      </c>
+      <c r="B907" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C907" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D907" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E907" t="str">
+        <v>15</v>
+      </c>
+      <c r="F907" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G907" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H907" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I907" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J907" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K907" t="str">
+        <v/>
+      </c>
+      <c r="L907" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="str">
+        <v>C2026.0907</v>
+      </c>
+      <c r="B908" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C908" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D908" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E908" t="str">
+        <v>15</v>
+      </c>
+      <c r="F908" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G908" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H908" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I908" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J908" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K908" t="str">
+        <v/>
+      </c>
+      <c r="L908" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="str">
+        <v>C2026.0908</v>
+      </c>
+      <c r="B909" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C909" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D909" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E909" t="str">
+        <v>15</v>
+      </c>
+      <c r="F909" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G909" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H909" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I909" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J909" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K909" t="str">
+        <v/>
+      </c>
+      <c r="L909" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="str">
+        <v>C2026.0909</v>
+      </c>
+      <c r="B910" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C910" t="str">
+        <v>53489448</v>
+      </c>
+      <c r="D910" t="str">
+        <v>SIDE SILL DX</v>
+      </c>
+      <c r="E910" t="str">
+        <v>15</v>
+      </c>
+      <c r="F910" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G910" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H910" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I910" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J910" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K910" t="str">
+        <v/>
+      </c>
+      <c r="L910" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="str">
+        <v>C2026.0910</v>
+      </c>
+      <c r="B911" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C911" t="str">
+        <v>53327793</v>
+      </c>
+      <c r="D911" t="str">
+        <v>REINF. BULKHEAD SX</v>
+      </c>
+      <c r="E911" t="str">
+        <v>15</v>
+      </c>
+      <c r="F911" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G911" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H911" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I911" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J911" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K911" t="str">
+        <v/>
+      </c>
+      <c r="L911" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="str">
+        <v>C2026.0911</v>
+      </c>
+      <c r="B912" t="str">
+        <v>08/04/2026</v>
+      </c>
+      <c r="C912" t="str">
+        <v>53327782</v>
+      </c>
+      <c r="D912" t="str">
+        <v>REINF. BULKHEAD DX</v>
+      </c>
+      <c r="E912" t="str">
+        <v>15</v>
+      </c>
+      <c r="F912" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G912" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H912" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I912" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J912" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K912" t="str">
+        <v/>
+      </c>
+      <c r="L912" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="str">
+        <v>C2026.0912</v>
+      </c>
+      <c r="B913" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C913" t="str">
+        <v>52225420</v>
+      </c>
+      <c r="D913" t="str">
+        <v>PONTEIRA SX</v>
+      </c>
+      <c r="E913" t="str">
+        <v>15</v>
+      </c>
+      <c r="F913" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G913" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H913" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I913" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J913" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K913" t="str">
+        <v/>
+      </c>
+      <c r="L913" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="str">
+        <v>C2026.0913</v>
+      </c>
+      <c r="B914" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C914" t="str">
+        <v>53376480</v>
+      </c>
+      <c r="D914" t="str">
+        <v>PONTEIRA DX</v>
+      </c>
+      <c r="E914" t="str">
+        <v>15</v>
+      </c>
+      <c r="F914" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G914" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H914" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I914" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J914" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K914" t="str">
+        <v/>
+      </c>
+      <c r="L914" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="str">
+        <v>C2026.0914</v>
+      </c>
+      <c r="B915" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C915" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D915" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E915" t="str">
+        <v>15</v>
+      </c>
+      <c r="F915" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G915" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H915" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I915" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J915" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K915" t="str">
+        <v/>
+      </c>
+      <c r="L915" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="str">
+        <v>C2026.0915</v>
+      </c>
+      <c r="B916" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C916" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D916" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E916" t="str">
+        <v>15</v>
+      </c>
+      <c r="F916" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G916" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H916" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I916" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J916" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K916" t="str">
+        <v/>
+      </c>
+      <c r="L916" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="str">
+        <v>C2026.0916</v>
+      </c>
+      <c r="B917" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C917" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D917" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E917" t="str">
+        <v>15</v>
+      </c>
+      <c r="F917" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G917" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H917" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I917" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J917" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K917" t="str">
+        <v/>
+      </c>
+      <c r="L917" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="str">
+        <v>C2026.0917</v>
+      </c>
+      <c r="B918" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C918" t="str">
+        <v>53489530</v>
+      </c>
+      <c r="D918" t="str">
+        <v>CALÇO 03 DX</v>
+      </c>
+      <c r="E918" t="str">
+        <v>15</v>
+      </c>
+      <c r="F918" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G918" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H918" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I918" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J918" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K918" t="str">
+        <v/>
+      </c>
+      <c r="L918" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="str">
+        <v>C2026.0918</v>
+      </c>
+      <c r="B919" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C919" t="str">
+        <v>53490336</v>
+      </c>
+      <c r="D919" t="str">
+        <v>CALÇO 01 DX</v>
+      </c>
+      <c r="E919" t="str">
+        <v>15</v>
+      </c>
+      <c r="F919" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G919" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H919" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I919" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J919" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K919" t="str">
+        <v/>
+      </c>
+      <c r="L919" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="str">
+        <v>C2026.0919</v>
+      </c>
+      <c r="B920" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C920" t="str">
+        <v>53490336</v>
+      </c>
+      <c r="D920" t="str">
+        <v>CALÇO 01 DX</v>
+      </c>
+      <c r="E920" t="str">
+        <v>15</v>
+      </c>
+      <c r="F920" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G920" t="str">
+        <v>matheus</v>
+      </c>
+      <c r="H920" t="str">
+        <v>1º TURNO</v>
+      </c>
+      <c r="I920" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J920" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K920" t="str">
+        <v/>
+      </c>
+      <c r="L920" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="str">
+        <v>C2026.0920</v>
+      </c>
+      <c r="B921" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C921" t="str">
+        <v>53359033</v>
+      </c>
+      <c r="D921" t="str">
+        <v>BRACKET RR FASCIA ATTACK SING</v>
+      </c>
+      <c r="E921" t="str">
+        <v>15</v>
+      </c>
+      <c r="F921" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G921" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H921" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I921" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J921" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K921" t="str">
+        <v/>
+      </c>
+      <c r="L921" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="str">
+        <v>C2026.0921</v>
+      </c>
+      <c r="B922" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C922" t="str">
+        <v>53359033</v>
+      </c>
+      <c r="D922" t="str">
+        <v>BRACKET RR FASCIA ATTACK SING</v>
+      </c>
+      <c r="E922" t="str">
+        <v>15</v>
+      </c>
+      <c r="F922" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G922" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H922" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I922" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J922" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K922" t="str">
+        <v/>
+      </c>
+      <c r="L922" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="str">
+        <v>C2026.0922</v>
+      </c>
+      <c r="B923" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C923" t="str">
+        <v>53359033</v>
+      </c>
+      <c r="D923" t="str">
+        <v>BRACKET RR FASCIA ATTACK SING</v>
+      </c>
+      <c r="E923" t="str">
+        <v>15</v>
+      </c>
+      <c r="F923" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G923" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H923" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I923" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J923" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K923" t="str">
+        <v/>
+      </c>
+      <c r="L923" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="str">
+        <v>C2026.0923</v>
+      </c>
+      <c r="B924" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C924" t="str">
+        <v>53359033</v>
+      </c>
+      <c r="D924" t="str">
+        <v>BRACKET RR FASCIA ATTACK SING</v>
+      </c>
+      <c r="E924" t="str">
+        <v>15</v>
+      </c>
+      <c r="F924" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G924" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H924" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I924" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J924" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K924" t="str">
+        <v/>
+      </c>
+      <c r="L924" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="str">
+        <v>C2026.0924</v>
+      </c>
+      <c r="B925" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C925" t="str">
+        <v>53359033</v>
+      </c>
+      <c r="D925" t="str">
+        <v>BRACKET RR FASCIA ATTACK SING</v>
+      </c>
+      <c r="E925" t="str">
+        <v>15</v>
+      </c>
+      <c r="F925" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G925" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H925" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I925" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J925" t="str">
+        <v>INSP LAYOUT</v>
+      </c>
+      <c r="K925" t="str">
+        <v/>
+      </c>
+      <c r="L925" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="str">
+        <v>C2026.0925</v>
+      </c>
+      <c r="B926" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C926" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D926" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E926" t="str">
+        <v>15</v>
+      </c>
+      <c r="F926" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G926" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H926" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I926" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J926" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K926" t="str">
+        <v/>
+      </c>
+      <c r="L926" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="str">
+        <v>C2026.0926</v>
+      </c>
+      <c r="B927" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C927" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D927" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E927" t="str">
+        <v>15</v>
+      </c>
+      <c r="F927" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G927" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H927" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I927" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J927" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K927" t="str">
+        <v/>
+      </c>
+      <c r="L927" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="str">
+        <v>C2026.0927</v>
+      </c>
+      <c r="B928" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C928" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D928" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E928" t="str">
+        <v>15</v>
+      </c>
+      <c r="F928" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G928" t="str">
+        <v>izaac</v>
+      </c>
+      <c r="H928" t="str">
+        <v>ADM</v>
+      </c>
+      <c r="I928" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J928" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K928" t="str">
+        <v/>
+      </c>
+      <c r="L928" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="str">
+        <v>C2026.0928</v>
+      </c>
+      <c r="B929" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C929" t="str">
+        <v>53490375</v>
+      </c>
+      <c r="D929" t="str">
+        <v>BARRA DE LIGAÇÃO SX</v>
+      </c>
+      <c r="E929" t="str">
+        <v>15</v>
+      </c>
+      <c r="F929" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G929" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H929" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I929" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J929" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K929" t="str">
+        <v/>
+      </c>
+      <c r="L929" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="str">
+        <v>C2026.0929</v>
+      </c>
+      <c r="B930" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C930" t="str">
+        <v>53490377</v>
+      </c>
+      <c r="D930" t="str">
+        <v>PEÇA DE LIGAÇÃO DX</v>
+      </c>
+      <c r="E930" t="str">
+        <v>15</v>
+      </c>
+      <c r="F930" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G930" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H930" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I930" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J930" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K930" t="str">
+        <v/>
+      </c>
+      <c r="L930" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="str">
+        <v>C2026.0930</v>
+      </c>
+      <c r="B931" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C931" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D931" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E931" t="str">
+        <v>15</v>
+      </c>
+      <c r="F931" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G931" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H931" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I931" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J931" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K931" t="str">
+        <v/>
+      </c>
+      <c r="L931" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="str">
+        <v>C2026.0931</v>
+      </c>
+      <c r="B932" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C932" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D932" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E932" t="str">
+        <v>15</v>
+      </c>
+      <c r="F932" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G932" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H932" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I932" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J932" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K932" t="str">
+        <v/>
+      </c>
+      <c r="L932" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="str">
+        <v>C2026.0932</v>
+      </c>
+      <c r="B933" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C933" t="str">
+        <v>53489671</v>
+      </c>
+      <c r="D933" t="str">
+        <v>CONJUNTO TRANSVERSAL TRASEIRO</v>
+      </c>
+      <c r="E933" t="str">
+        <v>15</v>
+      </c>
+      <c r="F933" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G933" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H933" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I933" t="str">
+        <v>CMM GLOBAL</v>
+      </c>
+      <c r="J933" t="str">
+        <v>GEOMETRIA</v>
+      </c>
+      <c r="K933" t="str">
+        <v/>
+      </c>
+      <c r="L933" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="str">
+        <v>C2026.0933</v>
+      </c>
+      <c r="B934" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C934" t="str">
+        <v>52213270</v>
+      </c>
+      <c r="D934" t="str">
+        <v>TORRESMO NEW LT</v>
+      </c>
+      <c r="E934">
+        <v>15</v>
+      </c>
+      <c r="F934" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G934" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H934" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I934" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J934" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K934" t="str">
+        <v/>
+      </c>
+      <c r="L934" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="str">
+        <v>C2026.0934</v>
+      </c>
+      <c r="B935" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C935" t="str">
+        <v>52213270</v>
+      </c>
+      <c r="D935" t="str">
+        <v>TORRESMO NEW LT</v>
+      </c>
+      <c r="E935">
+        <v>15</v>
+      </c>
+      <c r="F935" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G935" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H935" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I935" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J935" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K935" t="str">
+        <v/>
+      </c>
+      <c r="L935" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L861"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L935"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/relatorios.xlsx
+++ b/data/relatorios.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L935"/>
+  <dimension ref="A1:L938"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7081,7 +7081,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K176" t="str" xml:space="preserve">
-        <v xml:space="preserve">PREVENTIVA_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PREVENTIVA_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L176" t="b">
@@ -7804,7 +7804,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K195" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇA 02 DA BASE A1_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L195" t="b">
@@ -13885,7 +13885,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K355" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L355" t="b">
@@ -13924,7 +13924,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K356" t="str" xml:space="preserve">
-        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PEÇAS EM DESVIO_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L356" t="b">
@@ -23083,7 +23083,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K597" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L597" t="b">
@@ -23122,7 +23122,7 @@
         <v>ANÁLISE DIMENSIONAL</v>
       </c>
       <c r="K598" t="str" xml:space="preserve">
-        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d_
+        <v xml:space="preserve">PRODUÇÃO APÓS ATUAÇÃO DA FERRAMENTARIA_x000d__x000d__x000d__x000d__x000d__x000d_
 </v>
       </c>
       <c r="L598" t="b">
@@ -35872,7 +35872,7 @@
       <c r="D934" t="str">
         <v>TORRESMO NEW LT</v>
       </c>
-      <c r="E934">
+      <c r="E934" t="str">
         <v>15</v>
       </c>
       <c r="F934" t="str">
@@ -35910,7 +35910,7 @@
       <c r="D935" t="str">
         <v>TORRESMO NEW LT</v>
       </c>
-      <c r="E935">
+      <c r="E935" t="str">
         <v>15</v>
       </c>
       <c r="F935" t="str">
@@ -35932,12 +35932,126 @@
         <v/>
       </c>
       <c r="L935" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="str">
+        <v>C2026.0935</v>
+      </c>
+      <c r="B936" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C936" t="str">
+        <v>53489540</v>
+      </c>
+      <c r="D936" t="str">
+        <v>REINF CPL FRT CONNEC SUSP RR RT</v>
+      </c>
+      <c r="E936" t="str">
+        <v>15</v>
+      </c>
+      <c r="F936" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G936" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H936" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I936" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J936" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K936" t="str">
+        <v/>
+      </c>
+      <c r="L936" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="str">
+        <v>C2026.0936</v>
+      </c>
+      <c r="B937" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C937" t="str">
+        <v>53489595</v>
+      </c>
+      <c r="D937" t="str">
+        <v>REINF CPL FRT CONNEC SUSP RR LT</v>
+      </c>
+      <c r="E937" t="str">
+        <v>15</v>
+      </c>
+      <c r="F937" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G937" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H937" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I937" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J937" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K937" t="str">
+        <v/>
+      </c>
+      <c r="L937" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="str">
+        <v>C2026.0937</v>
+      </c>
+      <c r="B938" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="C938" t="str">
+        <v>53489595</v>
+      </c>
+      <c r="D938" t="str">
+        <v>REINF CPL FRT CONNEC SUSP RR LT</v>
+      </c>
+      <c r="E938" t="str">
+        <v>15</v>
+      </c>
+      <c r="F938" t="str">
+        <v>QUALIDADE</v>
+      </c>
+      <c r="G938" t="str">
+        <v>luis</v>
+      </c>
+      <c r="H938" t="str">
+        <v>2º TURNO</v>
+      </c>
+      <c r="I938" t="str">
+        <v>METRASCAN</v>
+      </c>
+      <c r="J938" t="str">
+        <v>ANÁLISE DIMENSIONAL</v>
+      </c>
+      <c r="K938" t="str">
+        <v/>
+      </c>
+      <c r="L938" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L935"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L938"/>
   </ignoredErrors>
 </worksheet>
 </file>